--- a/data/merged/2026-09-23/MERGED_JP_Wet-Dry-Floor-Washer_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_JP_Wet-Dry-Floor-Washer_2026-09-23.xlsx
@@ -4933,13 +4933,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4977,13 +4977,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5021,13 +5021,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5065,13 +5065,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5109,13 +5109,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5197,13 +5197,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5241,13 +5241,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5329,13 +5329,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6232,270 +6232,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId44" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Product 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId45" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Product 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Product 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6837,7 +6573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -10426,40 +10162,40 @@
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>B07221ZY3D</t>
+          <t>B09P2RKRWX</t>
         </is>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス</t>
+          <t>Tineco</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07221ZY3D&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B09P2RKRWX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス 干湿两用 商用 吸尘器 真空清洁器 MPV-201 容量20L 电线长度10m</t>
+          <t>Tineco Floor One S5 Plus 无线擦水吸尘器 干湿两用siLoop 智能传感器检测污垢,吸力强,自动清洁干燥,长时间运行,大容量水箱,2 年保修</t>
         </is>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07221ZY3D?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/51RoxZljqoL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>B07221ZY3D</t>
+          <t>B09P2RKRWX</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
@@ -10473,13 +10209,13 @@
         </is>
       </c>
       <c r="O16" s="13">
-        <v>9909</v>
+        <v>118602</v>
       </c>
       <c r="P16" s="13">
-        <v>-1706</v>
+        <v>-79702</v>
       </c>
       <c r="Q16" s="14">
-        <v>-0.21</v>
+        <v>-2.05</v>
       </c>
       <c r="R16" s="15" t="inlineStr">
         <is>
@@ -10488,86 +10224,80 @@
       </c>
       <c r="S16" s="16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T16" s="13">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="U16" s="14">
-        <v>-0.07</v>
+        <v>-0.1</v>
       </c>
       <c r="V16" s="13">
-        <v>1726340</v>
-      </c>
-      <c r="W16" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X16" s="13">
-        <v>658109</v>
-      </c>
+        <v>1599968</v>
+      </c>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
       <c r="Y16" s="17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="13">
-        <v>12980</v>
+        <v>49999</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16" s="2">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="AD16" s="17">
-        <v>259</v>
+        <v>3875</v>
       </c>
       <c r="AE16" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AG16" s="19">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="13">
         <v>1020</v>
       </c>
       <c r="AI16" s="14">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AJ16"/>
       <c r="AK16" s="11" t="inlineStr">
         <is>
-          <t>2017-06-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AL16" s="17">
-        <v>3376</v>
+        <v>847</v>
       </c>
       <c r="AM16" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN16" s="11"/>
       <c r="AO16" s="11"/>
       <c r="AP16"/>
       <c r="AQ16" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR16" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS16" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス【9月の連休について 休業日：9/20～9/23 ※ご注文は9/24より順次出荷】</t>
+          <t>Tineco公式ストア</t>
         </is>
       </c>
       <c r="AT16" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU16" s="11" t="inlineStr">
@@ -10577,20 +10307,16 @@
       </c>
       <c r="AV16" s="12" t="inlineStr">
         <is>
-          <t>豊前市 福岡県 8280031 JP</t>
+          <t>Yokohama-shi Kanagawa 220-0004 JP</t>
         </is>
       </c>
       <c r="AW16" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF</t>
         </is>
       </c>
       <c r="AX16" s="11"/>
-      <c r="AY16" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY16" s="11"/>
       <c r="AZ16" s="11"/>
       <c r="BA16" s="11"/>
       <c r="BB16" s="11"/>
@@ -10608,45 +10334,45 @@
       <c r="BF16" s="11"/>
       <c r="BG16" s="11"/>
       <c r="BH16" s="12"/>
-      <c r="BI16" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI16" s="20"/>
       <c r="BJ16" s="20" t="inlineStr">
         <is>
-          <t>8.5 Kilograms</t>
+          <t>7.88 kg</t>
         </is>
       </c>
       <c r="BK16" s="20" t="inlineStr">
         <is>
-          <t>8.50 kg</t>
+          <t>7.88 kg</t>
         </is>
       </c>
       <c r="BL16" s="20" t="inlineStr">
         <is>
-          <t>38長さ x 35幅 x 53高さ cm</t>
-        </is>
-      </c>
-      <c r="BM16" s="20"/>
+          <t>27.3 x 26 x 110 cm</t>
+        </is>
+      </c>
+      <c r="BM16" s="20" t="inlineStr">
+        <is>
+          <t>27.30 x 26.00 x 110.00 cm</t>
+        </is>
+      </c>
       <c r="BN16" s="20" t="inlineStr">
         <is>
-          <t>9 kg</t>
+          <t>7.89 kg</t>
         </is>
       </c>
       <c r="BO16" s="20" t="inlineStr">
         <is>
-          <t>9.00 kg</t>
+          <t>7.89 kg</t>
         </is>
       </c>
       <c r="BP16" s="20" t="inlineStr">
         <is>
-          <t>52.6 x 45.5 x 40 cm</t>
+          <t>66.7 x 32.4 x 29 cm</t>
         </is>
       </c>
       <c r="BQ16" s="20" t="inlineStr">
         <is>
-          <t>52.60 x 45.50 x 40.00 cm</t>
+          <t>66.70 x 32.40 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR16" s="11" t="inlineStr">
@@ -10662,40 +10388,40 @@
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>B09P2RKRWX</t>
+          <t>B0DPKHQMTK</t>
         </is>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Tineco</t>
+          <t>MOVA</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B09P2RKRWX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0DPKHQMTK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Tineco Floor One S5 Plus 无线擦水吸尘器 干湿两用siLoop 智能传感器检测污垢,吸力强,自动清洁干燥,长时间运行,大容量水箱,2 年保修</t>
+          <t>MOVA M10 擦水吸尘器 多功能于一台 自动清洗 自走式 干湿两用吸尘器 无线s180° 可平放,90° 可旋转 Tangle-Free™ 解决方案操作体验重量 0.9 kg 18,000 Pa 吸力消毒热风干燥 LED 显示屏语音指南大容量</t>
         </is>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DPKHQMTK?psc=1</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31n2eqDnquL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>B09P2RKRWX</t>
+          <t>B0DPKHQMTK</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
@@ -10709,13 +10435,13 @@
         </is>
       </c>
       <c r="O17" s="13">
-        <v>118602</v>
+        <v>27554</v>
       </c>
       <c r="P17" s="13">
-        <v>-79702</v>
+        <v>66371</v>
       </c>
       <c r="Q17" s="14">
-        <v>-2.05</v>
+        <v>0.65</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
@@ -10724,57 +10450,55 @@
       </c>
       <c r="S17" s="16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T17" s="13">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="U17" s="14">
-        <v>-0.1</v>
+        <v>-0.46</v>
       </c>
       <c r="V17" s="13">
-        <v>1599968</v>
+        <v>1307039</v>
       </c>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z17" s="13">
-        <v>49999</v>
+        <v>31879</v>
       </c>
       <c r="AA17"/>
       <c r="AB17"/>
-      <c r="AC17" s="2">
-        <v>91</v>
-      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" s="17">
-        <v>3875</v>
+        <v>546</v>
       </c>
       <c r="AE17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" s="18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG17" s="19">
-        <v>0</v>
+        <v>0.024399999999999998</v>
       </c>
       <c r="AH17" s="13">
-        <v>1020</v>
+        <v>1100</v>
       </c>
       <c r="AI17" s="14">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AJ17"/>
       <c r="AK17" s="11" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AL17" s="17">
-        <v>847</v>
+        <v>590</v>
       </c>
       <c r="AM17" s="11" t="inlineStr">
         <is>
@@ -10788,11 +10512,11 @@
         <v>10</v>
       </c>
       <c r="AR17" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS17" s="12" t="inlineStr">
         <is>
-          <t>Tineco公式ストア</t>
+          <t>MOVA Official</t>
         </is>
       </c>
       <c r="AT17" s="11" t="inlineStr">
@@ -10802,17 +10526,17 @@
       </c>
       <c r="AU17" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV17" s="12" t="inlineStr">
         <is>
-          <t>Yokohama-shi Kanagawa 220-0004 JP</t>
+          <t>HONG KONG 000 HK</t>
         </is>
       </c>
       <c r="AW17" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ</t>
         </is>
       </c>
       <c r="AX17" s="11"/>
@@ -10837,42 +10561,38 @@
       <c r="BI17" s="20"/>
       <c r="BJ17" s="20" t="inlineStr">
         <is>
-          <t>7.88 kg</t>
+          <t>4.4 Kilograms</t>
         </is>
       </c>
       <c r="BK17" s="20" t="inlineStr">
         <is>
-          <t>7.88 kg</t>
+          <t>4.40 kg</t>
         </is>
       </c>
       <c r="BL17" s="20" t="inlineStr">
         <is>
-          <t>27.3 x 26 x 110 cm</t>
-        </is>
-      </c>
-      <c r="BM17" s="20" t="inlineStr">
-        <is>
-          <t>27.30 x 26.00 x 110.00 cm</t>
-        </is>
-      </c>
+          <t>23.5長さ x 26.5幅 x 111.6高さ cm</t>
+        </is>
+      </c>
+      <c r="BM17" s="20"/>
       <c r="BN17" s="20" t="inlineStr">
         <is>
-          <t>7.89 kg</t>
+          <t>11.4 kg</t>
         </is>
       </c>
       <c r="BO17" s="20" t="inlineStr">
         <is>
-          <t>7.89 kg</t>
+          <t>11.40 kg</t>
         </is>
       </c>
       <c r="BP17" s="20" t="inlineStr">
         <is>
-          <t>66.7 x 32.4 x 29 cm</t>
+          <t>75 x 43 x 38 cm</t>
         </is>
       </c>
       <c r="BQ17" s="20" t="inlineStr">
         <is>
-          <t>66.70 x 32.40 x 29.00 cm</t>
+          <t>75.00 x 43.00 x 38.00 cm</t>
         </is>
       </c>
       <c r="BR17" s="11" t="inlineStr">
@@ -10888,40 +10608,40 @@
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>B0DPKHQMTK</t>
+          <t>B097SMD859</t>
         </is>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>MOVA</t>
+          <t>Tineco</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0DPKHQMTK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B097SMD859&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>MOVA M10 擦水吸尘器 多功能于一台 自动清洗 自走式 干湿两用吸尘器 无线s180° 可平放,90° 可旋转 Tangle-Free™ 解决方案操作体验重量 0.9 kg 18,000 Pa 吸力消毒热风干燥 LED 显示屏语音指南大容量</t>
+          <t>Tineco Tineco Floor One S5 Combo 无线轻量化 擦水吸尘器s可以打猎 | 配备 iLoop 智能传感器 | 自动拖把清洁和干燥 | 自走式&amp;长时间运行 | 兼容 WiFi 语音指南和应用程序连接 | 包括专用洗涤剂</t>
         </is>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DPKHQMTK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B097SMD859?psc=1</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31n2eqDnquL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71foMOvOBgL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>B0DPKHQMTK</t>
+          <t>B097SMD859</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr">
@@ -10935,13 +10655,13 @@
         </is>
       </c>
       <c r="O18" s="13">
-        <v>27554</v>
+        <v>38090</v>
       </c>
       <c r="P18" s="13">
-        <v>66371</v>
+        <v>34045</v>
       </c>
       <c r="Q18" s="14">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -10950,17 +10670,17 @@
       </c>
       <c r="S18" s="16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T18" s="13">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="U18" s="14">
-        <v>-0.46</v>
+        <v>-0.1</v>
       </c>
       <c r="V18" s="13">
-        <v>1307039</v>
+        <v>1215962</v>
       </c>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
@@ -10968,25 +10688,27 @@
         <v>3</v>
       </c>
       <c r="Z18" s="13">
-        <v>31879</v>
+        <v>31999</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
-      <c r="AC18" s="2"/>
+      <c r="AC18" s="2">
+        <v>91</v>
+      </c>
       <c r="AD18" s="17">
-        <v>546</v>
+        <v>383</v>
       </c>
       <c r="AE18" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="18">
         <v>4</v>
       </c>
       <c r="AG18" s="19">
-        <v>0.024399999999999998</v>
+        <v>0</v>
       </c>
       <c r="AH18" s="13">
-        <v>1100</v>
+        <v>1020</v>
       </c>
       <c r="AI18" s="14">
         <v>0.82</v>
@@ -10994,11 +10716,11 @@
       <c r="AJ18"/>
       <c r="AK18" s="11" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AL18" s="17">
-        <v>590</v>
+        <v>1866</v>
       </c>
       <c r="AM18" s="11" t="inlineStr">
         <is>
@@ -11016,7 +10738,7 @@
       </c>
       <c r="AS18" s="12" t="inlineStr">
         <is>
-          <t>MOVA Official</t>
+          <t>Tineco公式ストア</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
@@ -11026,21 +10748,25 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV18" s="12" t="inlineStr">
         <is>
-          <t>HONG KONG 000 HK</t>
+          <t>Yokohama-shi Kanagawa 220-0004 JP</t>
         </is>
       </c>
       <c r="AW18" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF</t>
         </is>
       </c>
       <c r="AX18" s="11"/>
-      <c r="AY18" s="11"/>
+      <c r="AY18" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ18" s="11"/>
       <c r="BA18" s="11"/>
       <c r="BB18" s="11"/>
@@ -11058,41 +10784,45 @@
       <c r="BF18" s="11"/>
       <c r="BG18" s="11"/>
       <c r="BH18" s="12"/>
-      <c r="BI18" s="20"/>
+      <c r="BI18" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ18" s="20" t="inlineStr">
         <is>
-          <t>4.4 Kilograms</t>
+          <t>6 kg</t>
         </is>
       </c>
       <c r="BK18" s="20" t="inlineStr">
         <is>
-          <t>4.40 kg</t>
+          <t>6.00 kg</t>
         </is>
       </c>
       <c r="BL18" s="20" t="inlineStr">
         <is>
-          <t>23.5長さ x 26.5幅 x 111.6高さ cm</t>
+          <t>33長さ x 28幅 x 67高さ cm</t>
         </is>
       </c>
       <c r="BM18" s="20"/>
       <c r="BN18" s="20" t="inlineStr">
         <is>
-          <t>11.4 kg</t>
+          <t>8.1 kg</t>
         </is>
       </c>
       <c r="BO18" s="20" t="inlineStr">
         <is>
-          <t>11.40 kg</t>
+          <t>8.10 kg</t>
         </is>
       </c>
       <c r="BP18" s="20" t="inlineStr">
         <is>
-          <t>75 x 43 x 38 cm</t>
+          <t>69.5 x 34.7 x 29.4 cm</t>
         </is>
       </c>
       <c r="BQ18" s="20" t="inlineStr">
         <is>
-          <t>75.00 x 43.00 x 38.00 cm</t>
+          <t>69.50 x 34.70 x 29.40 cm</t>
         </is>
       </c>
       <c r="BR18" s="11" t="inlineStr">
@@ -11108,40 +10838,40 @@
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>B097SMD859</t>
+          <t>B0DXY4BJ5K</t>
         </is>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Tineco</t>
+          <t>NARWAL(ナーワル)</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B097SMD859&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0DXY4BJ5K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Tineco Tineco Floor One S5 Combo 无线轻量化 擦水吸尘器s可以打猎 | 配备 iLoop 智能传感器 | 自动拖把清洁和干燥 | 自走式&amp;长时间运行 | 兼容 WiFi 语音指南和应用程序连接 | 包括专用洗涤剂</t>
+          <t>Narwal S20 Pro 无线擦地吸尘器 20,000Pa强力吸力 自动清洗s家用电器评论百思买,自走式,拖把自动清洁功能,干湿两用 家具下也可清洁地板、瓷砖、石地板专用 配备零缠结刷,非常适合有孩子和宠物的家庭 免维护</t>
         </is>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B097SMD859?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71foMOvOBgL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31yY5-X2isL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>B097SMD859</t>
+          <t>B0DXY4BJ5K</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
@@ -11155,13 +10885,13 @@
         </is>
       </c>
       <c r="O19" s="13">
-        <v>38090</v>
+        <v>30959</v>
       </c>
       <c r="P19" s="13">
-        <v>34045</v>
+        <v>24122</v>
       </c>
       <c r="Q19" s="14">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="R19" s="15" t="inlineStr">
         <is>
@@ -11170,61 +10900,59 @@
       </c>
       <c r="S19" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T19" s="13">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="U19" s="14">
-        <v>-0.1</v>
+        <v>-0.85</v>
       </c>
       <c r="V19" s="13">
-        <v>1215962</v>
+        <v>527688</v>
       </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="13">
-        <v>31999</v>
+        <v>58632</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
-      <c r="AC19" s="2">
-        <v>91</v>
-      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" s="17">
-        <v>383</v>
+        <v>62</v>
       </c>
       <c r="AE19" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" s="18">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG19" s="19">
-        <v>0</v>
+        <v>0.11109999999999999</v>
       </c>
       <c r="AH19" s="13">
         <v>1020</v>
       </c>
       <c r="AI19" s="14">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AJ19"/>
       <c r="AK19" s="11" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AL19" s="17">
-        <v>1866</v>
+        <v>579</v>
       </c>
       <c r="AM19" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN19" s="11"/>
@@ -11238,29 +10966,17 @@
       </c>
       <c r="AS19" s="12" t="inlineStr">
         <is>
-          <t>Tineco公式ストア</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT19" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU19" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV19" s="12" t="inlineStr">
-        <is>
-          <t>Yokohama-shi Kanagawa 220-0004 JP</t>
-        </is>
-      </c>
-      <c r="AW19" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU19" s="11"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="11"/>
       <c r="AX19" s="11"/>
       <c r="AY19" s="11" t="inlineStr">
         <is>
@@ -11291,38 +11007,38 @@
       </c>
       <c r="BJ19" s="20" t="inlineStr">
         <is>
-          <t>6 kg</t>
+          <t>7.84 Kilograms</t>
         </is>
       </c>
       <c r="BK19" s="20" t="inlineStr">
         <is>
-          <t>6.00 kg</t>
+          <t>7.84 kg</t>
         </is>
       </c>
       <c r="BL19" s="20" t="inlineStr">
         <is>
-          <t>33長さ x 28幅 x 67高さ cm</t>
+          <t>27.3長さ x 25.5幅 x 117.2高さ cm</t>
         </is>
       </c>
       <c r="BM19" s="20"/>
       <c r="BN19" s="20" t="inlineStr">
         <is>
-          <t>8.1 kg</t>
+          <t>7.84 kg</t>
         </is>
       </c>
       <c r="BO19" s="20" t="inlineStr">
         <is>
-          <t>8.10 kg</t>
+          <t>7.84 kg</t>
         </is>
       </c>
       <c r="BP19" s="20" t="inlineStr">
         <is>
-          <t>69.5 x 34.7 x 29.4 cm</t>
+          <t>74.1 x 34.2 x 28.9 cm</t>
         </is>
       </c>
       <c r="BQ19" s="20" t="inlineStr">
         <is>
-          <t>69.50 x 34.70 x 29.40 cm</t>
+          <t>74.10 x 34.20 x 28.90 cm</t>
         </is>
       </c>
       <c r="BR19" s="11" t="inlineStr">
@@ -11338,45 +11054,45 @@
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>B001N2FEV4</t>
+          <t>B0G4RMHHWV</t>
         </is>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>パオック(PAOCK)</t>
+          <t>SOLEMOOD</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%91%E3%82%AA%E3%83%83%E3%82%AFPAOCK/page/24D761D2-B57C-4143-A66C-A75C65189148?lp_asin=B001N2FEV4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/SOLEMOOD%E3%81%AB%E9%96%A2%E3%81%99%E3%82%8B%E5%AE%B6%E9%9B%BB%E8%A3%BD%E5%93%81%E3%81%AF%E3%81%93%E3%81%93%E3%81%8B%E3%82%89%E5%A7%8B%E3%82%81%E3%82%8B/page/4411883D-2ADD-48FC-8F7F-269EBDD113E8?lp_asin=B0G4RMHHWV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>【仅限在线购买】PAOCK (PAOCK) 不锈钢 双用途 吸尘器 干湿两用 吸入功率220W 海军蓝 20L 自动收缩电线 NVC-20L</t>
+          <t>【4个清洗头×17000Pa超强吸力地毯清洁器】 家用地毯清洁剂 漂浮污垢 布清洗机 浮起污垢强力吸力 去污 布清洗机 附带轻松进水口 沙发/地毯清洁剂 带去污功能 沙发/地毯/床垫/车内/玩偶/宠物垫 干湿两用 小巧(白)</t>
         </is>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B001N2FEV4?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31zQIeaA5fL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>B001N2FEV4</t>
+          <t>B0G4RMHHWV</t>
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>産業・研究開発用品:衛生・清掃用品:床・カーペットクリーニング:掃除機・アクセサリ:掃除機:乾湿両用掃除機</t>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="N20" s="12" t="inlineStr">
@@ -11385,13 +11101,13 @@
         </is>
       </c>
       <c r="O20" s="13">
-        <v>4321</v>
+        <v>102721</v>
       </c>
       <c r="P20" s="13">
-        <v>6752</v>
+        <v>-86656</v>
       </c>
       <c r="Q20" s="14">
-        <v>0.61</v>
+        <v>-5.39</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -11400,67 +11116,59 @@
       </c>
       <c r="S20" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T20" s="13">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="U20" s="14">
-        <v>0.55</v>
+        <v>-0.73</v>
       </c>
       <c r="V20" s="13">
-        <v>897858</v>
-      </c>
-      <c r="W20" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X20" s="13">
-        <v>575550</v>
-      </c>
+        <v>499257</v>
+      </c>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
       <c r="Y20" s="17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="13">
-        <v>73</v>
+        <v>15129</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
-      <c r="AC20" s="2">
-        <v>13</v>
-      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" s="17">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="AE20" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" s="18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG20" s="19">
-        <v>0</v>
+        <v>0.030299999999999997</v>
       </c>
       <c r="AH20" s="13">
-        <v>1020</v>
+        <v>781</v>
       </c>
       <c r="AI20" s="14">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="AJ20"/>
       <c r="AK20" s="11" t="inlineStr">
         <is>
-          <t>2012-07-03</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AL20" s="17">
-        <v>5194</v>
+        <v>271</v>
       </c>
       <c r="AM20" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN20" s="11"/>
@@ -11470,21 +11178,33 @@
         <v>10</v>
       </c>
       <c r="AR20" s="17">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AS20" s="12" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>SOLEMOOD正規販売店</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU20" s="11"/>
-      <c r="AV20" s="12"/>
-      <c r="AW20" s="11"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU20" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="AV20" s="12" t="inlineStr">
+        <is>
+          <t>大阪市 大阪府 5500027 JP</t>
+        </is>
+      </c>
+      <c r="AW20" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2L4LHXL144SJ</t>
+        </is>
+      </c>
       <c r="AX20" s="11"/>
       <c r="AY20" s="11" t="inlineStr">
         <is>
@@ -11499,7 +11219,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD20" s="11"/>
+      <c r="BD20" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE20" s="11"/>
       <c r="BF20" s="11"/>
       <c r="BG20" s="11"/>
@@ -11511,38 +11235,42 @@
       </c>
       <c r="BJ20" s="20" t="inlineStr">
         <is>
-          <t>5.7 Kilograms</t>
+          <t>5 Kilograms</t>
         </is>
       </c>
       <c r="BK20" s="20" t="inlineStr">
         <is>
-          <t>5.70 kg</t>
+          <t>5.00 kg</t>
         </is>
       </c>
       <c r="BL20" s="20" t="inlineStr">
         <is>
-          <t>36長さ x 36幅 x 53高さ cm</t>
-        </is>
-      </c>
-      <c r="BM20" s="20"/>
+          <t>46.5 x 36 x 24.5 cm</t>
+        </is>
+      </c>
+      <c r="BM20" s="20" t="inlineStr">
+        <is>
+          <t>46.50 x 36.00 x 24.50 cm</t>
+        </is>
+      </c>
       <c r="BN20" s="20" t="inlineStr">
         <is>
-          <t>8.27 kg</t>
+          <t>5 kg</t>
         </is>
       </c>
       <c r="BO20" s="20" t="inlineStr">
         <is>
-          <t>8.27 kg</t>
+          <t>5.00 kg</t>
         </is>
       </c>
       <c r="BP20" s="20" t="inlineStr">
         <is>
-          <t>57.6 x 38.9 x 38.1 cm</t>
+          <t>46.5 x 36 x 24.5 cm</t>
         </is>
       </c>
       <c r="BQ20" s="20" t="inlineStr">
         <is>
-          <t>57.60 x 38.90 x 38.10 cm</t>
+          <t>46.50 x 36.00 x 24.50 cm</t>
         </is>
       </c>
       <c r="BR20" s="11" t="inlineStr">
@@ -11558,45 +11286,45 @@
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>B0DXY4BJ5K</t>
+          <t>B0G1SGMXKS</t>
         </is>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>NARWAL(ナーワル)</t>
+          <t>REKNO</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0DXY4BJ5K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=REKNO</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Narwal S20 Pro 无线擦地吸尘器 20,000Pa强力吸力 自动清洗s家用电器评论百思买,自走式,拖把自动清洁功能,干湿两用 家具下也可清洁地板、瓷砖、石地板专用 配备零缠结刷,非常适合有孩子和宠物的家庭 免维护</t>
+          <t>【学习机构引入型号】充电式台式清洁器 [涡轮吸力×一键操作，轻松清理灰尘] 消铅笔屑清洁器 迷你桌面吸尘器 (黑色)</t>
         </is>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G1SGMXKS?psc=1</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31yY5-X2isL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41VCcIGen8L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>B0DXY4BJ5K</t>
+          <t>B0G1SGMXKS</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+          <t>ホーム＆キッチン:家電:生活家電:掃除機:ハンディクリーナー</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
@@ -11605,13 +11333,13 @@
         </is>
       </c>
       <c r="O21" s="13">
-        <v>30959</v>
+        <v>24342</v>
       </c>
       <c r="P21" s="13">
-        <v>24122</v>
+        <v>-11595</v>
       </c>
       <c r="Q21" s="14">
-        <v>0.18</v>
+        <v>-1.85</v>
       </c>
       <c r="R21" s="15" t="inlineStr">
         <is>
@@ -11620,84 +11348,106 @@
       </c>
       <c r="S21" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T21" s="13">
-        <v>9</v>
+        <v>249</v>
       </c>
       <c r="U21" s="14">
-        <v>-0.85</v>
+        <v>-0.22</v>
       </c>
       <c r="V21" s="13">
-        <v>527688</v>
-      </c>
-      <c r="W21" s="13"/>
-      <c r="X21" s="13"/>
+        <v>493020</v>
+      </c>
+      <c r="W21" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X21" s="13">
+        <v>99000</v>
+      </c>
       <c r="Y21" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z21" s="13">
-        <v>58632</v>
+        <v>1980</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="17">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="AE21" s="13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AF21" s="18">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AG21" s="19">
-        <v>0.11109999999999999</v>
+        <v>0.0482</v>
       </c>
       <c r="AH21" s="13">
-        <v>1020</v>
+        <v>415</v>
       </c>
       <c r="AI21" s="14">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AJ21"/>
       <c r="AK21" s="11" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AL21" s="17">
-        <v>579</v>
+        <v>311</v>
       </c>
       <c r="AM21" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN21" s="11"/>
       <c r="AO21" s="11"/>
       <c r="AP21"/>
       <c r="AQ21" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR21" s="17">
         <v>1</v>
       </c>
       <c r="AS21" s="12" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>REKNO公式</t>
         </is>
       </c>
       <c r="AT21" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU21" s="11"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="11"/>
-      <c r="AX21" s="11"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU21" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="AV21" s="12" t="inlineStr">
+        <is>
+          <t>茅ヶ崎 神奈川県 253-0056 JP</t>
+        </is>
+      </c>
+      <c r="AW21" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XMRK2V2774HR</t>
+        </is>
+      </c>
+      <c r="AX21" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AY21" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11727,43 +11477,43 @@
       </c>
       <c r="BJ21" s="20" t="inlineStr">
         <is>
-          <t>7.84 Kilograms</t>
+          <t>140 g</t>
         </is>
       </c>
       <c r="BK21" s="20" t="inlineStr">
         <is>
-          <t>7.84 kg</t>
+          <t>140.00 g</t>
         </is>
       </c>
       <c r="BL21" s="20" t="inlineStr">
         <is>
-          <t>27.3長さ x 25.5幅 x 117.2高さ cm</t>
+          <t>7.8長さ x 7.8幅 x 7.2高さ cm</t>
         </is>
       </c>
       <c r="BM21" s="20"/>
       <c r="BN21" s="20" t="inlineStr">
         <is>
-          <t>7.84 kg</t>
+          <t>140 g</t>
         </is>
       </c>
       <c r="BO21" s="20" t="inlineStr">
         <is>
-          <t>7.84 kg</t>
+          <t>140.00 g</t>
         </is>
       </c>
       <c r="BP21" s="20" t="inlineStr">
         <is>
-          <t>74.1 x 34.2 x 28.9 cm</t>
+          <t>8 x 7.8 x 7.5 cm</t>
         </is>
       </c>
       <c r="BQ21" s="20" t="inlineStr">
         <is>
-          <t>74.10 x 34.20 x 28.90 cm</t>
+          <t>8.00 x 7.80 x 7.50 cm</t>
         </is>
       </c>
       <c r="BR21" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -11774,163 +11524,159 @@
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>B0G4RMHHWV</t>
+          <t>B0FH4K7932</t>
         </is>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>SOLEMOOD</t>
+          <t>山善(YAMAZEN)</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/SOLEMOOD%E3%81%AB%E9%96%A2%E3%81%99%E3%82%8B%E5%AE%B6%E9%9B%BB%E8%A3%BD%E5%93%81%E3%81%AF%E3%81%93%E3%81%93%E3%81%8B%E3%82%89%E5%A7%8B%E3%82%81%E3%82%8B/page/4411883D-2ADD-48FC-8F7F-269EBDD113E8?lp_asin=B0G4RMHHWV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E5%B1%B1%E5%96%84YAMAZEN/page/7F62909C-AFC1-4B30-85C4-3B92BFA1D7EE?lp_asin=B0FH4K7932&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>【4个清洗头×17000Pa超强吸力地毯清洁器】 家用地毯清洁剂 漂浮污垢 布清洗机 浮起污垢强力吸力 去污 布清洗机 附带轻松进水口 沙发/地毯清洁剂 带去污功能 沙发/地毯/床垫/车内/玩偶/宠物垫 干湿两用 小巧(白)</t>
+          <t>【山善】手持清洁器 吸尘器 无线 手持吸尘器 干湿两用 车用 紧凑 小型 强吸引 银色 ZHK-WL10(S)</t>
         </is>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FH4K7932?psc=1</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61HCWRjyloL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>B0G4RMHHWV</t>
+          <t>B0FH4K7932</t>
         </is>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+          <t>ホーム＆キッチン:家電:生活家電:掃除機:ハンディクリーナー</t>
         </is>
       </c>
       <c r="N22" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン</t>
+          <t>ホーム＆キッチン</t>
         </is>
       </c>
       <c r="O22" s="13">
-        <v>102721</v>
+        <v>18078</v>
       </c>
       <c r="P22" s="13">
-        <v>-86656</v>
+        <v>-3733</v>
       </c>
       <c r="Q22" s="14">
-        <v>-5.39</v>
+        <v>-0.17</v>
       </c>
       <c r="R22" s="15" t="inlineStr">
         <is>
-          <t>ウェットドライショップ掃除機</t>
+          <t>ハンディクリーナー</t>
         </is>
       </c>
       <c r="S22" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T22" s="13">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="U22" s="14">
-        <v>-0.73</v>
+        <v>-0.19</v>
       </c>
       <c r="V22" s="13">
-        <v>499257</v>
-      </c>
-      <c r="W22" s="13"/>
-      <c r="X22" s="13"/>
+        <v>437320</v>
+      </c>
+      <c r="W22" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X22" s="13">
+        <v>168200</v>
+      </c>
       <c r="Y22" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z22" s="13">
-        <v>15129</v>
+        <v>3364</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
-      <c r="AC22" s="2"/>
+      <c r="AC22" s="2">
+        <v>3</v>
+      </c>
       <c r="AD22" s="17">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="AE22" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF22" s="18">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AG22" s="19">
-        <v>0.030299999999999997</v>
+        <v>0.0385</v>
       </c>
       <c r="AH22" s="13">
-        <v>781</v>
+        <v>472</v>
       </c>
       <c r="AI22" s="14">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="AJ22"/>
       <c r="AK22" s="11" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AL22" s="17">
-        <v>271</v>
+        <v>327</v>
       </c>
       <c r="AM22" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN22" s="11"/>
       <c r="AO22" s="11"/>
       <c r="AP22"/>
       <c r="AQ22" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR22" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS22" s="12" t="inlineStr">
         <is>
-          <t>SOLEMOOD正規販売店</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT22" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU22" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV22" s="12" t="inlineStr">
-        <is>
-          <t>大阪市 大阪府 5500027 JP</t>
-        </is>
-      </c>
-      <c r="AW22" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2L4LHXL144SJ</t>
-        </is>
-      </c>
-      <c r="AX22" s="11"/>
-      <c r="AY22" s="11" t="inlineStr">
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU22" s="11"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="11"/>
+      <c r="AX22" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="AY22" s="11"/>
       <c r="AZ22" s="11"/>
       <c r="BA22" s="11"/>
       <c r="BB22" s="11"/>
@@ -11948,54 +11694,50 @@
       <c r="BF22" s="11"/>
       <c r="BG22" s="11"/>
       <c r="BH22" s="12"/>
-      <c r="BI22" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI22" s="20"/>
       <c r="BJ22" s="20" t="inlineStr">
         <is>
-          <t>5 Kilograms</t>
+          <t>1.24 Kilograms</t>
         </is>
       </c>
       <c r="BK22" s="20" t="inlineStr">
         <is>
-          <t>5.00 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="BL22" s="20" t="inlineStr">
         <is>
-          <t>46.5 x 36 x 24.5 cm</t>
+          <t>8 x 40 x 7.8 cm</t>
         </is>
       </c>
       <c r="BM22" s="20" t="inlineStr">
         <is>
-          <t>46.50 x 36.00 x 24.50 cm</t>
+          <t>8.00 x 40.00 x 7.80 cm</t>
         </is>
       </c>
       <c r="BN22" s="20" t="inlineStr">
         <is>
-          <t>5 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="BO22" s="20" t="inlineStr">
         <is>
-          <t>5.00 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="BP22" s="20" t="inlineStr">
         <is>
-          <t>46.5 x 36 x 24.5 cm</t>
+          <t>42.7 x 14.8 x 10.4 cm</t>
         </is>
       </c>
       <c r="BQ22" s="20" t="inlineStr">
         <is>
-          <t>46.50 x 36.00 x 24.50 cm</t>
+          <t>42.70 x 14.80 x 10.40 cm</t>
         </is>
       </c>
       <c r="BR22" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -12006,45 +11748,45 @@
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>B0G1SGMXKS</t>
+          <t>B0DHV7QRSK</t>
         </is>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>REKNO</t>
+          <t>Vittorio(ヴィットリオ)</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=REKNO</t>
+          <t>https://www.amazon.co.jp/stores/Vittorio%E3%83%B4%E3%82%A3%E3%83%83%E3%83%88%E3%83%AA%E3%82%AA/page/EABDB95E-4F2B-4C11-AC74-31C4ED54290B?lp_asin=B0DHV7QRSK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>【学习机构引入型号】充电式台式清洁器 [涡轮吸力×一键操作，轻松清理灰尘] 消铅笔屑清洁器 迷你桌面吸尘器 (黑色)</t>
+          <t>维多利奥(Vittorio) 干湿两用清洁器 ZV-04-WD 【吸入功率65W 集尘约3.0L/吸水约1.5L】 小型紧凑型号(宽330×高310×深230mm) 主体重量2.5Kg 适合玄关・阳台清洁 现场简易清洁 可回收灰尘和污水s【吸込仕</t>
         </is>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0G1SGMXKS?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41VCcIGen8L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/4159pQjbgwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>B0G1SGMXKS</t>
+          <t>B0DHV7QRSK</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:ハンディクリーナー</t>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -12053,13 +11795,13 @@
         </is>
       </c>
       <c r="O23" s="13">
-        <v>24342</v>
+        <v>21824</v>
       </c>
       <c r="P23" s="13">
-        <v>-11595</v>
+        <v>69553</v>
       </c>
       <c r="Q23" s="14">
-        <v>-1.85</v>
+        <v>0.87</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -12068,106 +11810,88 @@
       </c>
       <c r="S23" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T23" s="13">
-        <v>249</v>
+        <v>64</v>
       </c>
       <c r="U23" s="14">
-        <v>-0.22</v>
+        <v>0.13</v>
       </c>
       <c r="V23" s="13">
-        <v>493020</v>
-      </c>
-      <c r="W23" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X23" s="13">
-        <v>99000</v>
-      </c>
+        <v>418880</v>
+      </c>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
       <c r="Y23" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="13">
-        <v>1980</v>
+        <v>42</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="17">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="AE23" s="13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AG23" s="19">
-        <v>0.0482</v>
+        <v>0</v>
       </c>
       <c r="AH23" s="13">
-        <v>415</v>
+        <v>675</v>
       </c>
       <c r="AI23" s="14">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AJ23"/>
       <c r="AK23" s="11" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AL23" s="17">
-        <v>311</v>
+        <v>700</v>
       </c>
       <c r="AM23" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN23" s="11"/>
       <c r="AO23" s="11"/>
       <c r="AP23"/>
       <c r="AQ23" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR23" s="17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AS23" s="12" t="inlineStr">
         <is>
-          <t>REKNO公式</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT23" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU23" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV23" s="12" t="inlineStr">
-        <is>
-          <t>茅ヶ崎 神奈川県 253-0056 JP</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU23" s="11"/>
+      <c r="AV23" s="12"/>
       <c r="AW23" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XMRK2V2774HR</t>
-        </is>
-      </c>
-      <c r="AX23" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UG91OLAXZDO3</t>
+        </is>
+      </c>
+      <c r="AX23" s="11"/>
       <c r="AY23" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12197,43 +11921,43 @@
       </c>
       <c r="BJ23" s="20" t="inlineStr">
         <is>
-          <t>140 g</t>
+          <t>2.5 Kilograms</t>
         </is>
       </c>
       <c r="BK23" s="20" t="inlineStr">
         <is>
-          <t>140.00 g</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL23" s="20" t="inlineStr">
         <is>
-          <t>7.8長さ x 7.8幅 x 7.2高さ cm</t>
+          <t>33長さ x 23幅 x 31高さ cm</t>
         </is>
       </c>
       <c r="BM23" s="20"/>
       <c r="BN23" s="20" t="inlineStr">
         <is>
-          <t>140 g</t>
+          <t>3.46 kg</t>
         </is>
       </c>
       <c r="BO23" s="20" t="inlineStr">
         <is>
-          <t>140.00 g</t>
+          <t>3.46 kg</t>
         </is>
       </c>
       <c r="BP23" s="20" t="inlineStr">
         <is>
-          <t>8 x 7.8 x 7.5 cm</t>
+          <t>35.5 x 32.9 x 24.5 cm</t>
         </is>
       </c>
       <c r="BQ23" s="20" t="inlineStr">
         <is>
-          <t>8.00 x 7.80 x 7.50 cm</t>
+          <t>35.50 x 32.90 x 24.50 cm</t>
         </is>
       </c>
       <c r="BR23" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -12244,40 +11968,40 @@
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>B0BW467WC5</t>
+          <t>B0GS4QDH7R</t>
         </is>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>longsafe</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Longsafe%E3%83%AD%E3%83%B3%E3%82%B0%E3%82%BB%E3%83%BC%E3%83%95/page/BD939425-D017-4A77-8C40-744607798C52?lp_asin=B0BW467WC5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Makita 牧田兼容品 充电式 集尘机 干湿两用 集尘机 业务用 粉尘用 鼓风机 软管 小型 吸 大容量 10L 吸尘器 无线 电动 18V 电池 对应 ※仅本体 电池 充电器 另售 (SYU01-BL)</t>
+          <t>uwant 擦水吸尘器 自动清洗 干湿两用吸尘器 热风干燥 电解水除菌 连续工作35分钟 大容量清污分离水箱 水花吸尘器 D100</t>
         </is>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BW467WC5?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41amhFEL1BL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>B0BW467WC5</t>
+          <t>B0GS4QDH7R</t>
         </is>
       </c>
       <c r="M24" s="12" t="inlineStr">
@@ -12291,13 +12015,13 @@
         </is>
       </c>
       <c r="O24" s="13">
-        <v>23820</v>
+        <v>128986</v>
       </c>
       <c r="P24" s="13">
-        <v>22670</v>
+        <v>-11178</v>
       </c>
       <c r="Q24" s="14">
-        <v>0.49</v>
+        <v>-0.09</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -12306,31 +12030,31 @@
       </c>
       <c r="S24" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T24" s="13">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="U24" s="14">
-        <v>0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="V24" s="13">
-        <v>448362</v>
+        <v>326508</v>
       </c>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="13">
-        <v>11799</v>
+        <v>11661</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="17">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="AE24" s="13">
         <v>0</v>
@@ -12342,69 +12066,69 @@
         <v>0</v>
       </c>
       <c r="AH24" s="13">
-        <v>675</v>
+        <v>1020</v>
       </c>
       <c r="AI24" s="14">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="AJ24"/>
       <c r="AK24" s="11" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AL24" s="17">
-        <v>1310</v>
+        <v>160</v>
       </c>
       <c r="AM24" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN24" s="11"/>
       <c r="AO24" s="11"/>
       <c r="AP24"/>
       <c r="AQ24" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR24" s="17">
         <v>1</v>
       </c>
       <c r="AS24" s="12" t="inlineStr">
         <is>
-          <t>YSJAPAN</t>
+          <t>Uwant公式ストア</t>
         </is>
       </c>
       <c r="AT24" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU24" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV24" s="12" t="inlineStr">
         <is>
-          <t>相模原市中央区 神奈川県 2520231 JP</t>
+          <t>深圳市 广东省 518000 CN</t>
         </is>
       </c>
       <c r="AW24" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21SFW0V5BVYM</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09</t>
         </is>
       </c>
       <c r="AX24" s="11"/>
-      <c r="AY24" s="11"/>
+      <c r="AY24" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ24" s="11"/>
       <c r="BA24" s="11"/>
       <c r="BB24" s="11"/>
-      <c r="BC24" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC24" s="11"/>
       <c r="BD24" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12414,41 +12138,45 @@
       <c r="BF24" s="11"/>
       <c r="BG24" s="11"/>
       <c r="BH24" s="12"/>
-      <c r="BI24" s="20"/>
+      <c r="BI24" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ24" s="20" t="inlineStr">
         <is>
-          <t>3.4 Kilograms</t>
+          <t>4.29 Kilograms</t>
         </is>
       </c>
       <c r="BK24" s="20" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
+          <t>4.29 kg</t>
         </is>
       </c>
       <c r="BL24" s="20" t="inlineStr">
         <is>
-          <t>40長さ x 25幅 x 26高さ cm</t>
+          <t>26.5長さ x 23.5幅 x 111.5高さ cm</t>
         </is>
       </c>
       <c r="BM24" s="20"/>
       <c r="BN24" s="20" t="inlineStr">
         <is>
-          <t>3.96 kg</t>
+          <t>4.29 kg</t>
         </is>
       </c>
       <c r="BO24" s="20" t="inlineStr">
         <is>
-          <t>3.96 kg</t>
+          <t>4.29 kg</t>
         </is>
       </c>
       <c r="BP24" s="20" t="inlineStr">
         <is>
-          <t>40.9 x 28.4 x 28 cm</t>
+          <t>72.5 x 31.2 x 29.1 cm</t>
         </is>
       </c>
       <c r="BQ24" s="20" t="inlineStr">
         <is>
-          <t>40.90 x 28.40 x 28.00 cm</t>
+          <t>72.50 x 31.20 x 29.10 cm</t>
         </is>
       </c>
       <c r="BR24" s="11" t="inlineStr">
@@ -12464,222 +12192,106 @@
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>B0FH4K7932</t>
+          <t>B001AHMQ90</t>
         </is>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>山善(YAMAZEN)</t>
-        </is>
-      </c>
+      <c r="F25" s="12"/>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E5%B1%B1%E5%96%84YAMAZEN/page/7F62909C-AFC1-4B30-85C4-3B92BFA1D7EE?lp_asin=B0FH4K7932&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>【山善】手持清洁器 吸尘器 无线 手持吸尘器 干湿两用 车用 紧凑 小型 强吸引 银色 ZHK-WL10(S)</t>
+          <t>Milwaukee 0880-20 18-Volt Cordless Wet/Dry Vacuum, Red</t>
         </is>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FH4K7932?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B001AHMQ90?psc=1</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61HCWRjyloL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/81jZdnaokeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>B0FH4K7932</t>
-        </is>
-      </c>
-      <c r="M25" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:ハンディクリーナー</t>
-        </is>
-      </c>
-      <c r="N25" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O25" s="13">
-        <v>18078</v>
-      </c>
-      <c r="P25" s="13">
-        <v>-3733</v>
-      </c>
-      <c r="Q25" s="14">
-        <v>-0.17</v>
-      </c>
-      <c r="R25" s="15" t="inlineStr">
-        <is>
-          <t>ハンディクリーナー</t>
-        </is>
-      </c>
-      <c r="S25" s="16" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="T25" s="13">
-        <v>130</v>
-      </c>
-      <c r="U25" s="14">
-        <v>-0.19</v>
-      </c>
-      <c r="V25" s="13">
-        <v>437320</v>
-      </c>
-      <c r="W25" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X25" s="13">
-        <v>168200</v>
-      </c>
-      <c r="Y25" s="17">
-        <v>2</v>
-      </c>
+          <t>B001AHMQ90</t>
+        </is>
+      </c>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="16"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="17"/>
       <c r="Z25" s="13">
-        <v>3364</v>
+        <v>183</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
-      <c r="AC25" s="2">
-        <v>3</v>
-      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" s="17">
-        <v>65</v>
-      </c>
-      <c r="AE25" s="13">
-        <v>5</v>
-      </c>
+        <v>3004</v>
+      </c>
+      <c r="AE25" s="13"/>
       <c r="AF25" s="18">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="AG25" s="19">
-        <v>0.0385</v>
-      </c>
-      <c r="AH25" s="13">
-        <v>472</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="13"/>
       <c r="AI25" s="14">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AJ25"/>
-      <c r="AK25" s="11" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AL25" s="17">
-        <v>327</v>
-      </c>
-      <c r="AM25" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK25" s="11"/>
+      <c r="AL25" s="17"/>
+      <c r="AM25" s="11"/>
       <c r="AN25" s="11"/>
       <c r="AO25" s="11"/>
       <c r="AP25"/>
-      <c r="AQ25" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR25" s="17">
-        <v>3</v>
-      </c>
-      <c r="AS25" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT25" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AQ25" s="17"/>
+      <c r="AR25" s="17"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="11"/>
       <c r="AU25" s="11"/>
       <c r="AV25" s="12"/>
       <c r="AW25" s="11"/>
-      <c r="AX25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AX25" s="11"/>
       <c r="AY25" s="11"/>
       <c r="AZ25" s="11"/>
       <c r="BA25" s="11"/>
       <c r="BB25" s="11"/>
-      <c r="BC25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC25" s="11"/>
+      <c r="BD25" s="11"/>
       <c r="BE25" s="11"/>
       <c r="BF25" s="11"/>
       <c r="BG25" s="11"/>
       <c r="BH25" s="12"/>
       <c r="BI25" s="20"/>
-      <c r="BJ25" s="20" t="inlineStr">
-        <is>
-          <t>1.24 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK25" s="20" t="inlineStr">
-        <is>
-          <t>1.24 kg</t>
-        </is>
-      </c>
-      <c r="BL25" s="20" t="inlineStr">
-        <is>
-          <t>8 x 40 x 7.8 cm</t>
-        </is>
-      </c>
-      <c r="BM25" s="20" t="inlineStr">
-        <is>
-          <t>8.00 x 40.00 x 7.80 cm</t>
-        </is>
-      </c>
-      <c r="BN25" s="20" t="inlineStr">
-        <is>
-          <t>1.24 kg</t>
-        </is>
-      </c>
-      <c r="BO25" s="20" t="inlineStr">
-        <is>
-          <t>1.24 kg</t>
-        </is>
-      </c>
-      <c r="BP25" s="20" t="inlineStr">
-        <is>
-          <t>42.7 x 14.8 x 10.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ25" s="20" t="inlineStr">
-        <is>
-          <t>42.70 x 14.80 x 10.40 cm</t>
-        </is>
-      </c>
-      <c r="BR25" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BJ25" s="20"/>
+      <c r="BK25" s="20"/>
+      <c r="BL25" s="20"/>
+      <c r="BM25" s="20"/>
+      <c r="BN25" s="20"/>
+      <c r="BO25" s="20"/>
+      <c r="BP25" s="20"/>
+      <c r="BQ25" s="20"/>
+      <c r="BR25" s="11"/>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
@@ -12688,218 +12300,106 @@
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>B0DHV7QRSK</t>
+          <t>B075MWCF8L</t>
         </is>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Vittorio(ヴィットリオ)</t>
-        </is>
-      </c>
+      <c r="F26" s="12"/>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Vittorio%E3%83%B4%E3%82%A3%E3%83%83%E3%83%88%E3%83%AA%E3%82%AA/page/EABDB95E-4F2B-4C11-AC74-31C4ED54290B?lp_asin=B0DHV7QRSK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>维多利奥(Vittorio) 干湿两用清洁器 ZV-04-WD 【吸入功率65W 集尘约3.0L/吸水约1.5L】 小型紧凑型号(宽330×高310×深230mm) 主体重量2.5Kg 适合玄关・阳台清洁 现场简易清洁 可回收灰尘和污水s【吸込仕</t>
+          <t>Shop-Vac 5989300 5-Gallon 4.5 Peak HP Stainless Steel Wet Dry Vacuum</t>
         </is>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B075MWCF8L?psc=1</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/4159pQjbgwL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/710AEFYSgZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>B0DHV7QRSK</t>
-        </is>
-      </c>
-      <c r="M26" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N26" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O26" s="13">
-        <v>21824</v>
-      </c>
-      <c r="P26" s="13">
-        <v>69553</v>
-      </c>
-      <c r="Q26" s="14">
-        <v>0.87</v>
-      </c>
-      <c r="R26" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S26" s="16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="T26" s="13">
-        <v>64</v>
-      </c>
-      <c r="U26" s="14">
-        <v>0.13</v>
-      </c>
-      <c r="V26" s="13">
-        <v>418880</v>
-      </c>
+          <t>B075MWCF8L</t>
+        </is>
+      </c>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="13"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="13"/>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
-      <c r="Y26" s="17">
-        <v>1</v>
-      </c>
+      <c r="Y26" s="17"/>
       <c r="Z26" s="13">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="17">
-        <v>29</v>
-      </c>
-      <c r="AE26" s="13">
-        <v>0</v>
-      </c>
+        <v>3416</v>
+      </c>
+      <c r="AE26" s="13"/>
       <c r="AF26" s="18">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG26" s="19">
         <v>0</v>
       </c>
-      <c r="AH26" s="13">
-        <v>675</v>
-      </c>
+      <c r="AH26" s="13"/>
       <c r="AI26" s="14">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AJ26"/>
-      <c r="AK26" s="11" t="inlineStr">
-        <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AL26" s="17">
-        <v>700</v>
-      </c>
-      <c r="AM26" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK26" s="11"/>
+      <c r="AL26" s="17"/>
+      <c r="AM26" s="11"/>
       <c r="AN26" s="11"/>
       <c r="AO26" s="11"/>
       <c r="AP26"/>
-      <c r="AQ26" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR26" s="17">
-        <v>10</v>
-      </c>
-      <c r="AS26" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT26" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AQ26" s="17"/>
+      <c r="AR26" s="17"/>
+      <c r="AS26" s="12"/>
+      <c r="AT26" s="11"/>
       <c r="AU26" s="11"/>
       <c r="AV26" s="12"/>
-      <c r="AW26" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UG91OLAXZDO3</t>
-        </is>
-      </c>
+      <c r="AW26" s="11"/>
       <c r="AX26" s="11"/>
-      <c r="AY26" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY26" s="11"/>
       <c r="AZ26" s="11"/>
       <c r="BA26" s="11"/>
       <c r="BB26" s="11"/>
-      <c r="BC26" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD26" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC26" s="11"/>
+      <c r="BD26" s="11"/>
       <c r="BE26" s="11"/>
       <c r="BF26" s="11"/>
       <c r="BG26" s="11"/>
       <c r="BH26" s="12"/>
-      <c r="BI26" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
-      <c r="BJ26" s="20" t="inlineStr">
-        <is>
-          <t>2.5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK26" s="20" t="inlineStr">
-        <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BL26" s="20" t="inlineStr">
-        <is>
-          <t>33長さ x 23幅 x 31高さ cm</t>
-        </is>
-      </c>
+      <c r="BI26" s="20"/>
+      <c r="BJ26" s="20"/>
+      <c r="BK26" s="20"/>
+      <c r="BL26" s="20"/>
       <c r="BM26" s="20"/>
-      <c r="BN26" s="20" t="inlineStr">
-        <is>
-          <t>3.46 kg</t>
-        </is>
-      </c>
-      <c r="BO26" s="20" t="inlineStr">
-        <is>
-          <t>3.46 kg</t>
-        </is>
-      </c>
-      <c r="BP26" s="20" t="inlineStr">
-        <is>
-          <t>35.5 x 32.9 x 24.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ26" s="20" t="inlineStr">
-        <is>
-          <t>35.50 x 32.90 x 24.50 cm</t>
-        </is>
-      </c>
-      <c r="BR26" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN26" s="20"/>
+      <c r="BO26" s="20"/>
+      <c r="BP26" s="20"/>
+      <c r="BQ26" s="20"/>
+      <c r="BR26" s="11"/>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
@@ -12908,222 +12408,104 @@
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>B0GS4QDH7R</t>
+          <t>B07KR2J116</t>
         </is>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>uwant</t>
-        </is>
-      </c>
+      <c r="F27" s="12"/>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>uwant 擦水吸尘器 自动清洗 干湿两用吸尘器 热风干燥 电解水除菌 连续工作35分钟 大容量清污分离水箱 水花吸尘器 D100</t>
+          <t>Minato 干湿两用 业务用 吸尘器 旋风式 真空吸尘器 MPV-151CY (容量15L/吸水0.5L)</t>
         </is>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07KR2J116?psc=1</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61+eOXLQJ5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>B0GS4QDH7R</t>
-        </is>
-      </c>
-      <c r="M27" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O27" s="13">
-        <v>128986</v>
-      </c>
-      <c r="P27" s="13">
-        <v>-11178</v>
-      </c>
-      <c r="Q27" s="14">
-        <v>-0.09</v>
-      </c>
-      <c r="R27" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S27" s="16" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="T27" s="13">
-        <v>28</v>
-      </c>
-      <c r="U27" s="14">
-        <v>-0.1</v>
-      </c>
-      <c r="V27" s="13">
-        <v>326508</v>
-      </c>
+          <t>B07KR2J116</t>
+        </is>
+      </c>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="13"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="13">
-        <v>11661</v>
-      </c>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="13"/>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="17">
-        <v>14</v>
-      </c>
-      <c r="AE27" s="13">
-        <v>0</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="AE27" s="13"/>
       <c r="AF27" s="18">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AG27" s="19">
         <v>0</v>
       </c>
-      <c r="AH27" s="13">
-        <v>1020</v>
-      </c>
+      <c r="AH27" s="13"/>
       <c r="AI27" s="14">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="AJ27"/>
-      <c r="AK27" s="11" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AL27" s="17">
-        <v>160</v>
-      </c>
-      <c r="AM27" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK27" s="11"/>
+      <c r="AL27" s="17"/>
+      <c r="AM27" s="11"/>
       <c r="AN27" s="11"/>
       <c r="AO27" s="11"/>
       <c r="AP27"/>
-      <c r="AQ27" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR27" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS27" s="12" t="inlineStr">
-        <is>
-          <t>Uwant公式ストア</t>
-        </is>
-      </c>
-      <c r="AT27" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU27" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV27" s="12" t="inlineStr">
-        <is>
-          <t>深圳市 广东省 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW27" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09</t>
-        </is>
-      </c>
+      <c r="AQ27" s="17"/>
+      <c r="AR27" s="17"/>
+      <c r="AS27" s="12"/>
+      <c r="AT27" s="11"/>
+      <c r="AU27" s="11"/>
+      <c r="AV27" s="12"/>
+      <c r="AW27" s="11"/>
       <c r="AX27" s="11"/>
-      <c r="AY27" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY27" s="11"/>
       <c r="AZ27" s="11"/>
       <c r="BA27" s="11"/>
       <c r="BB27" s="11"/>
       <c r="BC27" s="11"/>
-      <c r="BD27" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD27" s="11"/>
       <c r="BE27" s="11"/>
       <c r="BF27" s="11"/>
       <c r="BG27" s="11"/>
       <c r="BH27" s="12"/>
-      <c r="BI27" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
-      <c r="BJ27" s="20" t="inlineStr">
-        <is>
-          <t>4.29 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK27" s="20" t="inlineStr">
-        <is>
-          <t>4.29 kg</t>
-        </is>
-      </c>
-      <c r="BL27" s="20" t="inlineStr">
-        <is>
-          <t>26.5長さ x 23.5幅 x 111.5高さ cm</t>
-        </is>
-      </c>
+      <c r="BI27" s="20"/>
+      <c r="BJ27" s="20"/>
+      <c r="BK27" s="20"/>
+      <c r="BL27" s="20"/>
       <c r="BM27" s="20"/>
-      <c r="BN27" s="20" t="inlineStr">
-        <is>
-          <t>4.29 kg</t>
-        </is>
-      </c>
-      <c r="BO27" s="20" t="inlineStr">
-        <is>
-          <t>4.29 kg</t>
-        </is>
-      </c>
-      <c r="BP27" s="20" t="inlineStr">
-        <is>
-          <t>72.5 x 31.2 x 29.1 cm</t>
-        </is>
-      </c>
-      <c r="BQ27" s="20" t="inlineStr">
-        <is>
-          <t>72.50 x 31.20 x 29.10 cm</t>
-        </is>
-      </c>
-      <c r="BR27" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN27" s="20"/>
+      <c r="BO27" s="20"/>
+      <c r="BP27" s="20"/>
+      <c r="BQ27" s="20"/>
+      <c r="BR27" s="11"/>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
@@ -13132,92 +12514,62 @@
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>B0H993XND4</t>
+          <t>B08XLW562G</t>
         </is>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Gwrv</t>
-        </is>
-      </c>
+      <c r="F28" s="12"/>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Gwrv</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Gwrv 干湿两用 真空 带鼓风机功能 15L 家用 商用 吸尘器 800W (不锈钢制 标准型号(附9件套),18L)</t>
+          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
         </is>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H993XND4?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31OojZZwR0L._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/31NELDCajpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>B0H993XND4</t>
-        </is>
-      </c>
-      <c r="M28" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N28" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O28" s="13">
-        <v>217842</v>
-      </c>
-      <c r="P28" s="13">
-        <v>-116814</v>
-      </c>
-      <c r="Q28" s="14">
-        <v>-1.16</v>
-      </c>
-      <c r="R28" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S28" s="16" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="T28" s="13">
-        <v>3</v>
-      </c>
+          <t>B08XLW562G</t>
+        </is>
+      </c>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="13"/>
       <c r="U28" s="14"/>
-      <c r="V28" s="13">
-        <v>25197</v>
-      </c>
+      <c r="V28" s="13"/>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
-      <c r="Y28" s="17">
-        <v>9</v>
-      </c>
-      <c r="Z28" s="13">
-        <v>8399</v>
-      </c>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="13"/>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="2"/>
-      <c r="AD28" s="17"/>
+      <c r="AD28" s="17">
+        <v>3</v>
+      </c>
       <c r="AE28" s="13"/>
-      <c r="AF28" s="18"/>
+      <c r="AF28" s="18">
+        <v>2.7</v>
+      </c>
       <c r="AG28" s="19">
         <v>0</v>
       </c>
@@ -13228,45 +12580,17 @@
       <c r="AJ28"/>
       <c r="AK28" s="11"/>
       <c r="AL28" s="17"/>
-      <c r="AM28" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
+      <c r="AM28" s="11"/>
       <c r="AN28" s="11"/>
       <c r="AO28" s="11"/>
       <c r="AP28"/>
-      <c r="AQ28" s="17">
-        <v>6</v>
-      </c>
-      <c r="AR28" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS28" s="12" t="inlineStr">
-        <is>
-          <t>Gwrv直営店(5-9日以内にお届け)</t>
-        </is>
-      </c>
-      <c r="AT28" s="11" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU28" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV28" s="12" t="inlineStr">
-        <is>
-          <t>南京市 江苏省 211521 CN</t>
-        </is>
-      </c>
-      <c r="AW28" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1KH8VSASY5CZN</t>
-        </is>
-      </c>
+      <c r="AQ28" s="17"/>
+      <c r="AR28" s="17"/>
+      <c r="AS28" s="12"/>
+      <c r="AT28" s="11"/>
+      <c r="AU28" s="11"/>
+      <c r="AV28" s="12"/>
+      <c r="AW28" s="11"/>
       <c r="AX28" s="11"/>
       <c r="AY28" s="11"/>
       <c r="AZ28" s="11"/>
@@ -13279,21 +12603,9 @@
       <c r="BG28" s="11"/>
       <c r="BH28" s="12"/>
       <c r="BI28" s="20"/>
-      <c r="BJ28" s="20" t="inlineStr">
-        <is>
-          <t>2.9 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK28" s="20" t="inlineStr">
-        <is>
-          <t>2.90 kg</t>
-        </is>
-      </c>
-      <c r="BL28" s="20" t="inlineStr">
-        <is>
-          <t>33長さ x 33幅 x 42高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ28" s="20"/>
+      <c r="BK28" s="20"/>
+      <c r="BL28" s="20"/>
       <c r="BM28" s="20"/>
       <c r="BN28" s="20"/>
       <c r="BO28" s="20"/>
@@ -13308,7 +12620,7 @@
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>B001AHMQ90</t>
+          <t>B0C4HGZ1L6</t>
         </is>
       </c>
       <c r="D29" s="12"/>
@@ -13321,23 +12633,23 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee 0880-20 18-Volt Cordless Wet/Dry Vacuum, Red</t>
+          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
         </is>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B001AHMQ90?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/81jZdnaokeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>B001AHMQ90</t>
+          <t>B0C4HGZ1L6</t>
         </is>
       </c>
       <c r="M29" s="12"/>
@@ -13353,18 +12665,16 @@
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="17"/>
-      <c r="Z29" s="13">
-        <v>183</v>
-      </c>
+      <c r="Z29" s="13"/>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="17">
-        <v>3004</v>
+        <v>320</v>
       </c>
       <c r="AE29" s="13"/>
       <c r="AF29" s="18">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AG29" s="19">
         <v>0</v>
@@ -13416,7 +12726,7 @@
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>B075MWCF8L</t>
+          <t>B0CF9P7W51</t>
         </is>
       </c>
       <c r="D30" s="12"/>
@@ -13429,23 +12739,23 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Shop-Vac 5989300 5-Gallon 4.5 Peak HP Stainless Steel Wet Dry Vacuum</t>
+          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
         </is>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B075MWCF8L?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/710AEFYSgZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>B075MWCF8L</t>
+          <t>B0CF9P7W51</t>
         </is>
       </c>
       <c r="M30" s="12"/>
@@ -13461,18 +12771,16 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="17"/>
-      <c r="Z30" s="13">
-        <v>149</v>
-      </c>
+      <c r="Z30" s="13"/>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="17">
-        <v>3416</v>
+        <v>23</v>
       </c>
       <c r="AE30" s="13"/>
       <c r="AF30" s="18">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG30" s="19">
         <v>0</v>
@@ -13524,7 +12832,7 @@
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>B07KR2J116</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="D31" s="12"/>
@@ -13537,23 +12845,23 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Minato 干湿两用 业务用 吸尘器 旋风式 真空吸尘器 MPV-151CY (容量15L/吸水0.5L)</t>
+          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量</t>
         </is>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07KR2J116?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61+eOXLQJ5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>B07KR2J116</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="M31" s="12"/>
@@ -13574,11 +12882,11 @@
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="17">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AE31" s="13"/>
       <c r="AF31" s="18">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AG31" s="19">
         <v>0</v>
@@ -13630,7 +12938,7 @@
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>B08XLW562G</t>
+          <t>B0CPPHYW3B</t>
         </is>
       </c>
       <c r="D32" s="12"/>
@@ -13643,23 +12951,23 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
+          <t>Minato Works 干湿两用 吸尘器 真空吸尘器 MPV-101 +附带替换过滤器 水箱容量10升</t>
         </is>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31NELDCajpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71uxs5Aq9ML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>B08XLW562G</t>
+          <t>B0CPPHYW3B</t>
         </is>
       </c>
       <c r="M32" s="12"/>
@@ -13684,7 +12992,7 @@
       </c>
       <c r="AE32" s="13"/>
       <c r="AF32" s="18">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AG32" s="19">
         <v>0</v>
@@ -13736,7 +13044,7 @@
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>B0C4HGZ1L6</t>
+          <t>B0CYZFT9GT</t>
         </is>
       </c>
       <c r="D33" s="12"/>
@@ -13749,23 +13057,23 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
+          <t>Cretom(Cretom) 小巧型 2路电源 CG6</t>
         </is>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CYZFT9GT?psc=1</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61im7zODi8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>B0C4HGZ1L6</t>
+          <t>B0CYZFT9GT</t>
         </is>
       </c>
       <c r="M33" s="12"/>
@@ -13785,13 +13093,9 @@
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
-      <c r="AD33" s="17">
-        <v>320</v>
-      </c>
+      <c r="AD33" s="17"/>
       <c r="AE33" s="13"/>
-      <c r="AF33" s="18">
-        <v>4</v>
-      </c>
+      <c r="AF33" s="18"/>
       <c r="AG33" s="19">
         <v>0</v>
       </c>
@@ -13842,7 +13146,7 @@
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0CZKHJXNG</t>
         </is>
       </c>
       <c r="D34" s="12"/>
@@ -13855,23 +13159,23 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
+          <t>EUREKA NEY100 地毯清洁器 400W强力吸力 汽车座椅和布制品清洗 自洁式 地毯和沙发清洗 干湿两用 淋水清洗器 可用热水清洗 附带洗涤剂 三只刷子</t>
         </is>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71ZEEXdN4uL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0CZKHJXNG</t>
         </is>
       </c>
       <c r="M34" s="12"/>
@@ -13892,11 +13196,11 @@
       <c r="AB34"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="17">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="AE34" s="13"/>
       <c r="AF34" s="18">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AG34" s="19">
         <v>0</v>
@@ -13948,7 +13252,7 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B0D2VPQT2V</t>
         </is>
       </c>
       <c r="D35" s="12"/>
@@ -13961,23 +13265,23 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量</t>
+          <t>MOVA K10 Pro 湿拖吸尘器 自走式 湿拖2合1无绳棒吸尘器 可检测污垢 工作时0.9公斤超轻量 15000Pa强力吸力 干湿两用吸尘器 自动清洗 电解水除菌 30分钟连续工作 6毫米边缘清扫 大容量水箱 地板擦拭 LED显示屏 语音指南 家</t>
         </is>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B0D2VPQT2V</t>
         </is>
       </c>
       <c r="M35" s="12"/>
@@ -13998,11 +13302,11 @@
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="17">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="AE35" s="13"/>
       <c r="AF35" s="18">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AG35" s="19">
         <v>0</v>
@@ -14054,7 +13358,7 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B0CPPHYW3B</t>
+          <t>B0FGC7422M</t>
         </is>
       </c>
       <c r="D36" s="12"/>
@@ -14067,23 +13371,23 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Minato Works 干湿两用 吸尘器 真空吸尘器 MPV-101 +附带替换过滤器 水箱容量10升</t>
+          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
         </is>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71uxs5Aq9ML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0CPPHYW3B</t>
+          <t>B0FGC7422M</t>
         </is>
       </c>
       <c r="M36" s="12"/>
@@ -14104,11 +13408,11 @@
       <c r="AB36"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="17">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="AE36" s="13"/>
       <c r="AF36" s="18">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AG36" s="19">
         <v>0</v>
@@ -14160,7 +13464,7 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B0CYZFT9GT</t>
+          <t>B0FK9HN17M</t>
         </is>
       </c>
       <c r="D37" s="12"/>
@@ -14173,23 +13477,23 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Cretom(Cretom) 小巧型 2路电源 CG6</t>
+          <t>拖水式吸尘器 JONR ED12 Lite【日本最轻量】吸引・水洗・擦拭3合1 无绳式 推杆式吸尘器 20000Pa强力吸引 干湿两用 自动清洗 靠墙1mm清洁 长时间运行 大容量水箱 自立式&amp;自走式 拖把功能 适用于地板擦拭/硬质地板/地毯/缝隙</t>
         </is>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CYZFT9GT?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61im7zODi8L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>B0CYZFT9GT</t>
+          <t>B0FK9HN17M</t>
         </is>
       </c>
       <c r="M37" s="12"/>
@@ -14209,9 +13513,13 @@
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
-      <c r="AD37" s="17"/>
+      <c r="AD37" s="17">
+        <v>84</v>
+      </c>
       <c r="AE37" s="13"/>
-      <c r="AF37" s="18"/>
+      <c r="AF37" s="18">
+        <v>3.3</v>
+      </c>
       <c r="AG37" s="19">
         <v>0</v>
       </c>
@@ -14262,104 +13570,212 @@
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>B0CZKHJXNG</t>
+          <t>B0FL2KXDMX</t>
         </is>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>JONR</t>
+        </is>
+      </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpundefined</t>
+          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>EUREKA NEY100 地毯清洁器 400W强力吸力 汽车座椅和布制品清洗 自洁式 地毯和沙发清洗 干湿两用 淋水清洗器 可用热水清洗 附带洗涤剂 三只刷子</t>
+          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
         </is>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71ZEEXdN4uL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B0CZKHJXNG</t>
-        </is>
-      </c>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="16"/>
+          <t>B0FL2KXDMX</t>
+        </is>
+      </c>
+      <c r="M38" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="N38" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン</t>
+        </is>
+      </c>
+      <c r="O38" s="13">
+        <v>168676</v>
+      </c>
+      <c r="P38" s="13">
+        <v>1428</v>
+      </c>
+      <c r="Q38" s="14">
+        <v>0.01</v>
+      </c>
+      <c r="R38" s="15" t="inlineStr">
+        <is>
+          <t>ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="S38" s="16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="T38" s="13"/>
       <c r="U38" s="14"/>
       <c r="V38" s="13"/>
       <c r="W38" s="13"/>
       <c r="X38" s="13"/>
-      <c r="Y38" s="17"/>
-      <c r="Z38" s="13"/>
+      <c r="Y38" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="13">
+        <v>99990</v>
+      </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="17">
-        <v>152</v>
-      </c>
-      <c r="AE38" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="AE38" s="13">
+        <v>5</v>
+      </c>
       <c r="AF38" s="18">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AG38" s="19">
         <v>0</v>
       </c>
-      <c r="AH38" s="13"/>
+      <c r="AH38" s="13">
+        <v>781</v>
+      </c>
       <c r="AI38" s="14">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AJ38"/>
-      <c r="AK38" s="11"/>
-      <c r="AL38" s="17"/>
-      <c r="AM38" s="11"/>
+      <c r="AK38" s="11" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AL38" s="17">
+        <v>414</v>
+      </c>
+      <c r="AM38" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN38" s="11"/>
       <c r="AO38" s="11"/>
       <c r="AP38"/>
-      <c r="AQ38" s="17"/>
-      <c r="AR38" s="17"/>
-      <c r="AS38" s="12"/>
-      <c r="AT38" s="11"/>
-      <c r="AU38" s="11"/>
-      <c r="AV38" s="12"/>
-      <c r="AW38" s="11"/>
+      <c r="AQ38" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR38" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS38" s="12" t="inlineStr">
+        <is>
+          <t>JONR JP</t>
+        </is>
+      </c>
+      <c r="AT38" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU38" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV38" s="12" t="inlineStr">
+        <is>
+          <t>孝感市 湖北 432400 CN</t>
+        </is>
+      </c>
+      <c r="AW38" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC</t>
+        </is>
+      </c>
       <c r="AX38" s="11"/>
       <c r="AY38" s="11"/>
       <c r="AZ38" s="11"/>
       <c r="BA38" s="11"/>
       <c r="BB38" s="11"/>
-      <c r="BC38" s="11"/>
-      <c r="BD38" s="11"/>
+      <c r="BC38" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD38" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE38" s="11"/>
       <c r="BF38" s="11"/>
       <c r="BG38" s="11"/>
       <c r="BH38" s="12"/>
       <c r="BI38" s="20"/>
-      <c r="BJ38" s="20"/>
-      <c r="BK38" s="20"/>
-      <c r="BL38" s="20"/>
+      <c r="BJ38" s="20" t="inlineStr">
+        <is>
+          <t>6 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK38" s="20" t="inlineStr">
+        <is>
+          <t>6.00 kg</t>
+        </is>
+      </c>
+      <c r="BL38" s="20" t="inlineStr">
+        <is>
+          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
+        </is>
+      </c>
       <c r="BM38" s="20"/>
-      <c r="BN38" s="20"/>
-      <c r="BO38" s="20"/>
-      <c r="BP38" s="20"/>
-      <c r="BQ38" s="20"/>
-      <c r="BR38" s="11"/>
+      <c r="BN38" s="20" t="inlineStr">
+        <is>
+          <t>6 kg</t>
+        </is>
+      </c>
+      <c r="BO38" s="20" t="inlineStr">
+        <is>
+          <t>6.00 kg</t>
+        </is>
+      </c>
+      <c r="BP38" s="20" t="inlineStr">
+        <is>
+          <t>55.1 x 33.6 x 31.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ38" s="20" t="inlineStr">
+        <is>
+          <t>55.10 x 33.60 x 31.20 cm</t>
+        </is>
+      </c>
+      <c r="BR38" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
@@ -14368,7 +13784,7 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0D2VPQT2V</t>
+          <t>B0FPXLZSWP</t>
         </is>
       </c>
       <c r="D39" s="12"/>
@@ -14381,23 +13797,23 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>MOVA K10 Pro 湿拖吸尘器 自走式 湿拖2合1无绳棒吸尘器 可检测污垢 工作时0.9公斤超轻量 15000Pa强力吸力 干湿两用吸尘器 自动清洗 电解水除菌 30分钟连续工作 6毫米边缘清扫 大容量水箱 地板擦拭 LED显示屏 语音指南 家</t>
+          <t>Narwal S30 无线擦地吸尘器 20,000Pa吸力 一次性垃圾网s自走式 80℃ 温水拖把自动清洁热熨斗干燥干湿两用吸尘器,家具下方也可清洁,防缠结功能非常适合有儿童和宠物的家庭,无需维护,易于清洁</t>
         </is>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0D2VPQT2V</t>
+          <t>B0FPXLZSWP</t>
         </is>
       </c>
       <c r="M39" s="12"/>
@@ -14413,16 +13829,18 @@
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
       <c r="Y39" s="17"/>
-      <c r="Z39" s="13"/>
+      <c r="Z39" s="13">
+        <v>349</v>
+      </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="17">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="AE39" s="13"/>
       <c r="AF39" s="18">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AG39" s="19">
         <v>0</v>
@@ -14474,7 +13892,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
+          <t>B0FTLDNXKS</t>
         </is>
       </c>
       <c r="D40" s="12"/>
@@ -14487,23 +13905,23 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
+          <t>macros 2way 紧凑型手持吸尘器 Sramo MEH-172</t>
         </is>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FTLDNXKS?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/2198xIu6DlL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
+          <t>B0FTLDNXKS</t>
         </is>
       </c>
       <c r="M40" s="12"/>
@@ -14523,13 +13941,9 @@
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
-      <c r="AD40" s="17">
-        <v>29</v>
-      </c>
+      <c r="AD40" s="17"/>
       <c r="AE40" s="13"/>
-      <c r="AF40" s="18">
-        <v>3.8</v>
-      </c>
+      <c r="AF40" s="18"/>
       <c r="AG40" s="19">
         <v>0</v>
       </c>
@@ -14580,7 +13994,7 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0FHP2HN6D</t>
+          <t>B0GXDDCQ3M</t>
         </is>
       </c>
       <c r="D41" s="12"/>
@@ -14593,23 +14007,23 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>业务用 吸尘器 干湿两用 带吹风机 充电式 真空吸尘器 集尘机 无绳 电池 工业用 业务用 家庭用 普通家庭 办公室 公司 大容量 大清扫 (20L)</t>
+          <t>YTE PRO [2026新上市 400W 强力吸力] 支持60°C热水 自动清洗 去污 干湿两用 吸尘器 布清洗机 沙发/地毯/布制品/车内/毛绒玩具/羽绒外套/缝隙 移动方便 便于保养 日本国内PSE&amp;METI认证</t>
         </is>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FHP2HN6D?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71oZRUgvCTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B0FHP2HN6D</t>
+          <t>B0GXDDCQ3M</t>
         </is>
       </c>
       <c r="M41" s="12"/>
@@ -14629,13 +14043,9 @@
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
-      <c r="AD41" s="17">
-        <v>6</v>
-      </c>
+      <c r="AD41" s="17"/>
       <c r="AE41" s="13"/>
-      <c r="AF41" s="18">
-        <v>4.5</v>
-      </c>
+      <c r="AF41" s="18"/>
       <c r="AG41" s="19">
         <v>0</v>
       </c>
@@ -14686,7 +14096,7 @@
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>B0FK9HN17M</t>
+          <t>B0H6DZMNPV</t>
         </is>
       </c>
       <c r="D42" s="12"/>
@@ -14699,23 +14109,23 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>拖水式吸尘器 JONR ED12 Lite【日本最轻量】吸引・水洗・擦拭3合1 无绳式 推杆式吸尘器 20000Pa强力吸引 干湿两用 自动清洗 靠墙1mm清洁 长时间运行 大容量水箱 自立式&amp;自走式 拖把功能 适用于地板擦拭/硬质地板/地毯/缝隙</t>
+          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
         </is>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61FvOi4+ZDL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0FK9HN17M</t>
+          <t>B0H6DZMNPV</t>
         </is>
       </c>
       <c r="M42" s="12"/>
@@ -14735,13 +14145,9 @@
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
-      <c r="AD42" s="17">
-        <v>84</v>
-      </c>
+      <c r="AD42" s="17"/>
       <c r="AE42" s="13"/>
-      <c r="AF42" s="18">
-        <v>3.3</v>
-      </c>
+      <c r="AF42" s="18"/>
       <c r="AG42" s="19">
         <v>0</v>
       </c>
@@ -14792,212 +14198,100 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
+          <t>B0HGLFDYL5</t>
         </is>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>JONR</t>
-        </is>
-      </c>
+      <c r="F43" s="12"/>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
+          <t>Dyson(ダイソン) 吸尘器 无线 Dyson V12s Detect Slim Submarine (SV46 SU) 棒 手持式吸尘器 气旋 可用水擦拭 干式吸尘器 带充电支架 【从现在开始用水擦拭】 (New V8 slim)</t>
         </is>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51OBVYbKFFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
-        </is>
-      </c>
-      <c r="M43" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N43" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O43" s="13">
-        <v>168676</v>
-      </c>
-      <c r="P43" s="13">
-        <v>1428</v>
-      </c>
-      <c r="Q43" s="14">
-        <v>0.01</v>
-      </c>
-      <c r="R43" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S43" s="16" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>B0HGLFDYL5</t>
+        </is>
+      </c>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="16"/>
       <c r="T43" s="13"/>
       <c r="U43" s="14"/>
       <c r="V43" s="13"/>
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
-      <c r="Y43" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="13">
-        <v>99990</v>
-      </c>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="13"/>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
-      <c r="AD43" s="17">
-        <v>27</v>
-      </c>
-      <c r="AE43" s="13">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="18">
-        <v>3.5</v>
-      </c>
+      <c r="AD43" s="17"/>
+      <c r="AE43" s="13"/>
+      <c r="AF43" s="18"/>
       <c r="AG43" s="19">
         <v>0</v>
       </c>
-      <c r="AH43" s="13">
-        <v>781</v>
-      </c>
+      <c r="AH43" s="13"/>
       <c r="AI43" s="14">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AJ43"/>
-      <c r="AK43" s="11" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AL43" s="17">
-        <v>414</v>
-      </c>
-      <c r="AM43" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK43" s="11"/>
+      <c r="AL43" s="17"/>
+      <c r="AM43" s="11"/>
       <c r="AN43" s="11"/>
       <c r="AO43" s="11"/>
       <c r="AP43"/>
-      <c r="AQ43" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR43" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS43" s="12" t="inlineStr">
-        <is>
-          <t>JONR JP</t>
-        </is>
-      </c>
-      <c r="AT43" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU43" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV43" s="12" t="inlineStr">
-        <is>
-          <t>孝感市 湖北 432400 CN</t>
-        </is>
-      </c>
-      <c r="AW43" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC</t>
-        </is>
-      </c>
+      <c r="AQ43" s="17"/>
+      <c r="AR43" s="17"/>
+      <c r="AS43" s="12"/>
+      <c r="AT43" s="11"/>
+      <c r="AU43" s="11"/>
+      <c r="AV43" s="12"/>
+      <c r="AW43" s="11"/>
       <c r="AX43" s="11"/>
       <c r="AY43" s="11"/>
       <c r="AZ43" s="11"/>
       <c r="BA43" s="11"/>
       <c r="BB43" s="11"/>
-      <c r="BC43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC43" s="11"/>
+      <c r="BD43" s="11"/>
       <c r="BE43" s="11"/>
       <c r="BF43" s="11"/>
       <c r="BG43" s="11"/>
       <c r="BH43" s="12"/>
       <c r="BI43" s="20"/>
-      <c r="BJ43" s="20" t="inlineStr">
-        <is>
-          <t>6 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK43" s="20" t="inlineStr">
-        <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BL43" s="20" t="inlineStr">
-        <is>
-          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ43" s="20"/>
+      <c r="BK43" s="20"/>
+      <c r="BL43" s="20"/>
       <c r="BM43" s="20"/>
-      <c r="BN43" s="20" t="inlineStr">
-        <is>
-          <t>6 kg</t>
-        </is>
-      </c>
-      <c r="BO43" s="20" t="inlineStr">
-        <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BP43" s="20" t="inlineStr">
-        <is>
-          <t>55.1 x 33.6 x 31.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ43" s="20" t="inlineStr">
-        <is>
-          <t>55.10 x 33.60 x 31.20 cm</t>
-        </is>
-      </c>
-      <c r="BR43" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN43" s="20"/>
+      <c r="BO43" s="20"/>
+      <c r="BP43" s="20"/>
+      <c r="BQ43" s="20"/>
+      <c r="BR43" s="11"/>
     </row>
     <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
@@ -15006,7 +14300,7 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="D44" s="12"/>
@@ -15019,23 +14313,23 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Narwal S30 无线擦地吸尘器 20,000Pa吸力 一次性垃圾网s自走式 80℃ 温水拖把自动清洁热熨斗干燥干湿两用吸尘器,家具下方也可清洁,防缠结功能非常适合有儿童和宠物的家庭,无需维护,易于清洁</t>
+          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
         </is>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="M44" s="12"/>
@@ -15051,19 +14345,13 @@
       <c r="W44" s="13"/>
       <c r="X44" s="13"/>
       <c r="Y44" s="17"/>
-      <c r="Z44" s="13">
-        <v>349</v>
-      </c>
+      <c r="Z44" s="13"/>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="2"/>
-      <c r="AD44" s="17">
-        <v>41</v>
-      </c>
+      <c r="AD44" s="17"/>
       <c r="AE44" s="13"/>
-      <c r="AF44" s="18">
-        <v>3.6</v>
-      </c>
+      <c r="AF44" s="18"/>
       <c r="AG44" s="19">
         <v>0</v>
       </c>
@@ -15114,7 +14402,7 @@
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>B0FTLDNXKS</t>
+          <t>B0HHN61KPZ</t>
         </is>
       </c>
       <c r="D45" s="12"/>
@@ -15127,23 +14415,23 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>macros 2way 紧凑型手持吸尘器 Sramo MEH-172</t>
+          <t>Dyson(ダイソン) Dyson V12s Detect Slim Submarine 无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
         </is>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FTLDNXKS?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/2198xIu6DlL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41ItordAnnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>B0FTLDNXKS</t>
+          <t>B0HHN61KPZ</t>
         </is>
       </c>
       <c r="M45" s="12"/>
@@ -15208,618 +14496,6 @@
       <c r="BP45" s="20"/>
       <c r="BQ45" s="20"/>
       <c r="BR45" s="11"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>45</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>B0GXDDCQ3M</t>
-        </is>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>YTE PRO [2026新上市 400W 强力吸力] 支持60°C热水 自动清洗 去污 干湿两用 吸尘器 布清洗机 沙发/地毯/布制品/车内/毛绒玩具/羽绒外套/缝隙 移动方便 便于保养 日本国内PSE&amp;METI认证</t>
-        </is>
-      </c>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>B0GXDDCQ3M</t>
-        </is>
-      </c>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="13"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="17"/>
-      <c r="Z46" s="13"/>
-      <c r="AA46"/>
-      <c r="AB46"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="13"/>
-      <c r="AF46" s="18"/>
-      <c r="AG46" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="13"/>
-      <c r="AI46" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="11"/>
-      <c r="AL46" s="17"/>
-      <c r="AM46" s="11"/>
-      <c r="AN46" s="11"/>
-      <c r="AO46" s="11"/>
-      <c r="AP46"/>
-      <c r="AQ46" s="17"/>
-      <c r="AR46" s="17"/>
-      <c r="AS46" s="12"/>
-      <c r="AT46" s="11"/>
-      <c r="AU46" s="11"/>
-      <c r="AV46" s="12"/>
-      <c r="AW46" s="11"/>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="11"/>
-      <c r="BB46" s="11"/>
-      <c r="BC46" s="11"/>
-      <c r="BD46" s="11"/>
-      <c r="BE46" s="11"/>
-      <c r="BF46" s="11"/>
-      <c r="BG46" s="11"/>
-      <c r="BH46" s="12"/>
-      <c r="BI46" s="20"/>
-      <c r="BJ46" s="20"/>
-      <c r="BK46" s="20"/>
-      <c r="BL46" s="20"/>
-      <c r="BM46" s="20"/>
-      <c r="BN46" s="20"/>
-      <c r="BO46" s="20"/>
-      <c r="BP46" s="20"/>
-      <c r="BQ46" s="20"/>
-      <c r="BR46" s="11"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>B0H6DZMNPV</t>
-        </is>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
-        </is>
-      </c>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61FvOi4+ZDL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>B0H6DZMNPV</t>
-        </is>
-      </c>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="13"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="17"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47"/>
-      <c r="AB47"/>
-      <c r="AC47" s="2"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="18"/>
-      <c r="AG47" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="13"/>
-      <c r="AI47" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="11"/>
-      <c r="AL47" s="17"/>
-      <c r="AM47" s="11"/>
-      <c r="AN47" s="11"/>
-      <c r="AO47" s="11"/>
-      <c r="AP47"/>
-      <c r="AQ47" s="17"/>
-      <c r="AR47" s="17"/>
-      <c r="AS47" s="12"/>
-      <c r="AT47" s="11"/>
-      <c r="AU47" s="11"/>
-      <c r="AV47" s="12"/>
-      <c r="AW47" s="11"/>
-      <c r="AX47" s="11"/>
-      <c r="AY47" s="11"/>
-      <c r="AZ47" s="11"/>
-      <c r="BA47" s="11"/>
-      <c r="BB47" s="11"/>
-      <c r="BC47" s="11"/>
-      <c r="BD47" s="11"/>
-      <c r="BE47" s="11"/>
-      <c r="BF47" s="11"/>
-      <c r="BG47" s="11"/>
-      <c r="BH47" s="12"/>
-      <c r="BI47" s="20"/>
-      <c r="BJ47" s="20"/>
-      <c r="BK47" s="20"/>
-      <c r="BL47" s="20"/>
-      <c r="BM47" s="20"/>
-      <c r="BN47" s="20"/>
-      <c r="BO47" s="20"/>
-      <c r="BP47" s="20"/>
-      <c r="BQ47" s="20"/>
-      <c r="BR47" s="11"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>B0HGLFDYL5</t>
-        </is>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>Dyson(ダイソン) 吸尘器 无线 Dyson V12s Detect Slim Submarine (SV46 SU) 棒 手持式吸尘器 气旋 可用水擦拭 干式吸尘器 带充电支架 【从现在开始用水擦拭】 (New V8 slim)</t>
-        </is>
-      </c>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51OBVYbKFFL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>B0HGLFDYL5</t>
-        </is>
-      </c>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="17"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48"/>
-      <c r="AB48"/>
-      <c r="AC48" s="2"/>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="13"/>
-      <c r="AF48" s="18"/>
-      <c r="AG48" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="13"/>
-      <c r="AI48" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="11"/>
-      <c r="AL48" s="17"/>
-      <c r="AM48" s="11"/>
-      <c r="AN48" s="11"/>
-      <c r="AO48" s="11"/>
-      <c r="AP48"/>
-      <c r="AQ48" s="17"/>
-      <c r="AR48" s="17"/>
-      <c r="AS48" s="12"/>
-      <c r="AT48" s="11"/>
-      <c r="AU48" s="11"/>
-      <c r="AV48" s="12"/>
-      <c r="AW48" s="11"/>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48" s="20"/>
-      <c r="BJ48" s="20"/>
-      <c r="BK48" s="20"/>
-      <c r="BL48" s="20"/>
-      <c r="BM48" s="20"/>
-      <c r="BN48" s="20"/>
-      <c r="BO48" s="20"/>
-      <c r="BP48" s="20"/>
-      <c r="BQ48" s="20"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>B0HGLNPJPC</t>
-        </is>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
-        </is>
-      </c>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>B0HGLNPJPC</t>
-        </is>
-      </c>
-      <c r="M49" s="12"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="14"/>
-      <c r="R49" s="15"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="17"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49"/>
-      <c r="AB49"/>
-      <c r="AC49" s="2"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="11"/>
-      <c r="AL49" s="17"/>
-      <c r="AM49" s="11"/>
-      <c r="AN49" s="11"/>
-      <c r="AO49" s="11"/>
-      <c r="AP49"/>
-      <c r="AQ49" s="17"/>
-      <c r="AR49" s="17"/>
-      <c r="AS49" s="12"/>
-      <c r="AT49" s="11"/>
-      <c r="AU49" s="11"/>
-      <c r="AV49" s="12"/>
-      <c r="AW49" s="11"/>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="11"/>
-      <c r="BB49" s="11"/>
-      <c r="BC49" s="11"/>
-      <c r="BD49" s="11"/>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11"/>
-      <c r="BG49" s="11"/>
-      <c r="BH49" s="12"/>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20"/>
-      <c r="BK49" s="20"/>
-      <c r="BL49" s="20"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49" s="20"/>
-      <c r="BO49" s="20"/>
-      <c r="BP49" s="20"/>
-      <c r="BQ49" s="20"/>
-      <c r="BR49" s="11"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0HGQBZGVX</t>
-        </is>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>Sailozai 高出力家庭用掃除機、目地シーリング用キャニスター型掃除機、乾湿両用多目的強力 (18L ステンレス製 [9点セット])s800Wの強力な吸引力で水とホコリをしっかり除去 15/18Lの大容量で、頻繁なゴミ捨ては不要 複数のろ過シ</t>
-        </is>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HGQBZGVX?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51sDx2mVMXL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0HGQBZGVX</t>
-        </is>
-      </c>
-      <c r="M50" s="12"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="17"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="17"/>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="18"/>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="13"/>
-      <c r="AI50" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="11"/>
-      <c r="AL50" s="17"/>
-      <c r="AM50" s="11"/>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="17"/>
-      <c r="AR50" s="17"/>
-      <c r="AS50" s="12"/>
-      <c r="AT50" s="11"/>
-      <c r="AU50" s="11"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="11"/>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11"/>
-      <c r="BD50" s="11"/>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="20"/>
-      <c r="BJ50" s="20"/>
-      <c r="BK50" s="20"/>
-      <c r="BL50" s="20"/>
-      <c r="BM50" s="20"/>
-      <c r="BN50" s="20"/>
-      <c r="BO50" s="20"/>
-      <c r="BP50" s="20"/>
-      <c r="BQ50" s="20"/>
-      <c r="BR50" s="11"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0HHN61KPZ</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>Dyson(ダイソン) Dyson V12s Detect Slim Submarine 无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41ItordAnnL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0HHN61KPZ</t>
-        </is>
-      </c>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="17"/>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="18"/>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51" s="11"/>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17"/>
-      <c r="AS51" s="12"/>
-      <c r="AT51" s="11"/>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15935,233 +14611,192 @@
     <hyperlink ref="M15" r:id="rId108" tooltip="https://www.amazon.co.jp/b?node=218875650051"/>
     <hyperlink ref="N15" r:id="rId109"/>
     <hyperlink ref="AW15" r:id="rId110" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89"/>
-    <hyperlink ref="C16" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B07221ZY3D"/>
-    <hyperlink ref="G16" r:id="rId112" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07221ZY3D&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J16" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B07221ZY3D?psc=1"/>
-    <hyperlink ref="K16" r:id="rId114" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/51RoxZljqoL._AC_US600_.jpg"/>
-    <hyperlink ref="L16" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B07221ZY3D"/>
+    <hyperlink ref="C16" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
+    <hyperlink ref="G16" r:id="rId112" tooltip="https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B09P2RKRWX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J16" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1"/>
+    <hyperlink ref="K16" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_US600_.jpg"/>
+    <hyperlink ref="L16" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
     <hyperlink ref="M16" r:id="rId116" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N16" r:id="rId117"/>
-    <hyperlink ref="AW16" r:id="rId118" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
-    <hyperlink ref="C17" r:id="rId119" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
-    <hyperlink ref="G17" r:id="rId120" tooltip="https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B09P2RKRWX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J17" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1"/>
-    <hyperlink ref="K17" r:id="rId122" tooltip="https://images-na.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_US600_.jpg"/>
-    <hyperlink ref="L17" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
+    <hyperlink ref="AW16" r:id="rId118" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF"/>
+    <hyperlink ref="C17" r:id="rId119" tooltip="https://www.amazon.co.jp/dp/B0DPKHQMTK"/>
+    <hyperlink ref="G17" r:id="rId120" tooltip="https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0DPKHQMTK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J17" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B0DPKHQMTK?psc=1"/>
+    <hyperlink ref="K17" r:id="rId122" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31n2eqDnquL._AC_US600_.jpg"/>
+    <hyperlink ref="L17" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B0DPKHQMTK"/>
     <hyperlink ref="M17" r:id="rId124" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N17" r:id="rId125"/>
-    <hyperlink ref="AW17" r:id="rId126" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF"/>
-    <hyperlink ref="C18" r:id="rId127" tooltip="https://www.amazon.co.jp/dp/B0DPKHQMTK"/>
-    <hyperlink ref="G18" r:id="rId128" tooltip="https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0DPKHQMTK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J18" r:id="rId129" tooltip="https://www.amazon.co.jp/dp/B0DPKHQMTK?psc=1"/>
-    <hyperlink ref="K18" r:id="rId130" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31n2eqDnquL._AC_US600_.jpg"/>
-    <hyperlink ref="L18" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B0DPKHQMTK"/>
+    <hyperlink ref="AW17" r:id="rId126" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ"/>
+    <hyperlink ref="C18" r:id="rId127" tooltip="https://www.amazon.co.jp/dp/B097SMD859"/>
+    <hyperlink ref="G18" r:id="rId128" tooltip="https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B097SMD859&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J18" r:id="rId129" tooltip="https://www.amazon.co.jp/dp/B097SMD859?psc=1"/>
+    <hyperlink ref="K18" r:id="rId130" tooltip="https://images-na.ssl-images-amazon.com/images/I/71foMOvOBgL._AC_US600_.jpg"/>
+    <hyperlink ref="L18" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B097SMD859"/>
     <hyperlink ref="M18" r:id="rId132" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N18" r:id="rId133"/>
-    <hyperlink ref="AW18" r:id="rId134" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ"/>
-    <hyperlink ref="C19" r:id="rId135" tooltip="https://www.amazon.co.jp/dp/B097SMD859"/>
-    <hyperlink ref="G19" r:id="rId136" tooltip="https://www.amazon.co.jp/stores/Tineco/page/ADCCB8EF-CFF4-47C9-AAD4-1A5C1BB4039C?lp_asin=B097SMD859&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J19" r:id="rId137" tooltip="https://www.amazon.co.jp/dp/B097SMD859?psc=1"/>
-    <hyperlink ref="K19" r:id="rId138" tooltip="https://images-na.ssl-images-amazon.com/images/I/71foMOvOBgL._AC_US600_.jpg"/>
-    <hyperlink ref="L19" r:id="rId139" tooltip="https://www.amazon.co.jp/dp/B097SMD859"/>
+    <hyperlink ref="AW18" r:id="rId134" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF"/>
+    <hyperlink ref="C19" r:id="rId135" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
+    <hyperlink ref="G19" r:id="rId136" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0DXY4BJ5K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J19" r:id="rId137" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1"/>
+    <hyperlink ref="K19" r:id="rId138" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31yY5-X2isL._AC_US600_.jpg"/>
+    <hyperlink ref="L19" r:id="rId139" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
     <hyperlink ref="M19" r:id="rId140" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N19" r:id="rId141"/>
-    <hyperlink ref="AW19" r:id="rId142" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AAQX1XAXKAORF"/>
-    <hyperlink ref="C20" r:id="rId143" tooltip="https://www.amazon.co.jp/dp/B001N2FEV4"/>
-    <hyperlink ref="G20" r:id="rId144" tooltip="https://www.amazon.co.jp/stores/%E3%83%91%E3%82%AA%E3%83%83%E3%82%AFPAOCK/page/24D761D2-B57C-4143-A66C-A75C65189148?lp_asin=B001N2FEV4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J20" r:id="rId145" tooltip="https://www.amazon.co.jp/dp/B001N2FEV4?psc=1"/>
-    <hyperlink ref="K20" r:id="rId146" tooltip="https://m.media-amazon.com/images/I/31zQIeaA5fL._AC_US600_.jpg"/>
-    <hyperlink ref="L20" r:id="rId147" tooltip="https://www.amazon.co.jp/dp/B001N2FEV4"/>
-    <hyperlink ref="M20" r:id="rId148" tooltip="https://www.amazon.co.jp/b?node=3450851051"/>
-    <hyperlink ref="N20" r:id="rId149"/>
-    <hyperlink ref="C21" r:id="rId150" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
-    <hyperlink ref="G21" r:id="rId151" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0DXY4BJ5K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J21" r:id="rId152" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1"/>
-    <hyperlink ref="K21" r:id="rId153" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31yY5-X2isL._AC_US600_.jpg"/>
-    <hyperlink ref="L21" r:id="rId154" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
-    <hyperlink ref="M21" r:id="rId155" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="C20" r:id="rId142" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
+    <hyperlink ref="G20" r:id="rId143" tooltip="https://www.amazon.co.jp/stores/SOLEMOOD%E3%81%AB%E9%96%A2%E3%81%99%E3%82%8B%E5%AE%B6%E9%9B%BB%E8%A3%BD%E5%93%81%E3%81%AF%E3%81%93%E3%81%93%E3%81%8B%E3%82%89%E5%A7%8B%E3%82%81%E3%82%8B/page/4411883D-2ADD-48FC-8F7F-269EBDD113E8?lp_asin=B0G4RMHHWV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J20" r:id="rId144" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1"/>
+    <hyperlink ref="K20" r:id="rId145" tooltip="https://images-na.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_US600_.jpg"/>
+    <hyperlink ref="L20" r:id="rId146" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
+    <hyperlink ref="M20" r:id="rId147" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N20" r:id="rId148"/>
+    <hyperlink ref="AW20" r:id="rId149" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2L4LHXL144SJ"/>
+    <hyperlink ref="C21" r:id="rId150" tooltip="https://www.amazon.co.jp/dp/B0G1SGMXKS"/>
+    <hyperlink ref="G21" r:id="rId151" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=REKNO"/>
+    <hyperlink ref="J21" r:id="rId152" tooltip="https://www.amazon.co.jp/dp/B0G1SGMXKS?psc=1"/>
+    <hyperlink ref="K21" r:id="rId153" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41VCcIGen8L._AC_US600_.jpg"/>
+    <hyperlink ref="L21" r:id="rId154" tooltip="https://www.amazon.co.jp/dp/B0G1SGMXKS"/>
+    <hyperlink ref="M21" r:id="rId155" tooltip="https://www.amazon.co.jp/b?node=4083111"/>
     <hyperlink ref="N21" r:id="rId156"/>
-    <hyperlink ref="C22" r:id="rId157" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
-    <hyperlink ref="G22" r:id="rId158" tooltip="https://www.amazon.co.jp/stores/SOLEMOOD%E3%81%AB%E9%96%A2%E3%81%99%E3%82%8B%E5%AE%B6%E9%9B%BB%E8%A3%BD%E5%93%81%E3%81%AF%E3%81%93%E3%81%93%E3%81%8B%E3%82%89%E5%A7%8B%E3%82%81%E3%82%8B/page/4411883D-2ADD-48FC-8F7F-269EBDD113E8?lp_asin=B0G4RMHHWV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J22" r:id="rId159" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1"/>
-    <hyperlink ref="K22" r:id="rId160" tooltip="https://images-na.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_US600_.jpg"/>
-    <hyperlink ref="L22" r:id="rId161" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
-    <hyperlink ref="M22" r:id="rId162" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N22" r:id="rId163"/>
-    <hyperlink ref="AW22" r:id="rId164" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2L4LHXL144SJ"/>
-    <hyperlink ref="C23" r:id="rId165" tooltip="https://www.amazon.co.jp/dp/B0G1SGMXKS"/>
-    <hyperlink ref="G23" r:id="rId166" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=REKNO"/>
-    <hyperlink ref="J23" r:id="rId167" tooltip="https://www.amazon.co.jp/dp/B0G1SGMXKS?psc=1"/>
-    <hyperlink ref="K23" r:id="rId168" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41VCcIGen8L._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId169" tooltip="https://www.amazon.co.jp/dp/B0G1SGMXKS"/>
-    <hyperlink ref="M23" r:id="rId170" tooltip="https://www.amazon.co.jp/b?node=4083111"/>
+    <hyperlink ref="AW21" r:id="rId157" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XMRK2V2774HR"/>
+    <hyperlink ref="C22" r:id="rId158" tooltip="https://www.amazon.co.jp/dp/B0FH4K7932"/>
+    <hyperlink ref="G22" r:id="rId159" tooltip="https://www.amazon.co.jp/stores/%E5%B1%B1%E5%96%84YAMAZEN/page/7F62909C-AFC1-4B30-85C4-3B92BFA1D7EE?lp_asin=B0FH4K7932&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J22" r:id="rId160" tooltip="https://www.amazon.co.jp/dp/B0FH4K7932?psc=1"/>
+    <hyperlink ref="K22" r:id="rId161" tooltip="https://images-na.ssl-images-amazon.com/images/I/61HCWRjyloL._AC_US600_.jpg"/>
+    <hyperlink ref="L22" r:id="rId162" tooltip="https://www.amazon.co.jp/dp/B0FH4K7932"/>
+    <hyperlink ref="M22" r:id="rId163" tooltip="https://www.amazon.co.jp/b?node=4083111"/>
+    <hyperlink ref="N22" r:id="rId164"/>
+    <hyperlink ref="C23" r:id="rId165" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
+    <hyperlink ref="G23" r:id="rId166" tooltip="https://www.amazon.co.jp/stores/Vittorio%E3%83%B4%E3%82%A3%E3%83%83%E3%83%88%E3%83%AA%E3%82%AA/page/EABDB95E-4F2B-4C11-AC74-31C4ED54290B?lp_asin=B0DHV7QRSK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J23" r:id="rId167" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1"/>
+    <hyperlink ref="K23" r:id="rId168" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/4159pQjbgwL._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId169" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
+    <hyperlink ref="M23" r:id="rId170" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N23" r:id="rId171"/>
-    <hyperlink ref="AW23" r:id="rId172" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1XMRK2V2774HR"/>
-    <hyperlink ref="C24" r:id="rId173" tooltip="https://www.amazon.co.jp/dp/B0BW467WC5"/>
-    <hyperlink ref="G24" r:id="rId174" tooltip="https://www.amazon.co.jp/stores/Longsafe%E3%83%AD%E3%83%B3%E3%82%B0%E3%82%BB%E3%83%BC%E3%83%95/page/BD939425-D017-4A77-8C40-744607798C52?lp_asin=B0BW467WC5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId175" tooltip="https://www.amazon.co.jp/dp/B0BW467WC5?psc=1"/>
-    <hyperlink ref="K24" r:id="rId176" tooltip="https://m.media-amazon.com/images/I/41amhFEL1BL._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId177" tooltip="https://www.amazon.co.jp/dp/B0BW467WC5"/>
+    <hyperlink ref="AW23" r:id="rId172" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UG91OLAXZDO3"/>
+    <hyperlink ref="C24" r:id="rId173" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
+    <hyperlink ref="G24" r:id="rId174" tooltip="https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J24" r:id="rId175" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1"/>
+    <hyperlink ref="K24" r:id="rId176" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId177" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
     <hyperlink ref="M24" r:id="rId178" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N24" r:id="rId179"/>
-    <hyperlink ref="AW24" r:id="rId180" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21SFW0V5BVYM"/>
-    <hyperlink ref="C25" r:id="rId181" tooltip="https://www.amazon.co.jp/dp/B0FH4K7932"/>
-    <hyperlink ref="G25" r:id="rId182" tooltip="https://www.amazon.co.jp/stores/%E5%B1%B1%E5%96%84YAMAZEN/page/7F62909C-AFC1-4B30-85C4-3B92BFA1D7EE?lp_asin=B0FH4K7932&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J25" r:id="rId183" tooltip="https://www.amazon.co.jp/dp/B0FH4K7932?psc=1"/>
-    <hyperlink ref="K25" r:id="rId184" tooltip="https://images-na.ssl-images-amazon.com/images/I/61HCWRjyloL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId185" tooltip="https://www.amazon.co.jp/dp/B0FH4K7932"/>
-    <hyperlink ref="M25" r:id="rId186" tooltip="https://www.amazon.co.jp/b?node=4083111"/>
-    <hyperlink ref="N25" r:id="rId187"/>
-    <hyperlink ref="C26" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
-    <hyperlink ref="G26" r:id="rId189" tooltip="https://www.amazon.co.jp/stores/Vittorio%E3%83%B4%E3%82%A3%E3%83%83%E3%83%88%E3%83%AA%E3%82%AA/page/EABDB95E-4F2B-4C11-AC74-31C4ED54290B?lp_asin=B0DHV7QRSK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J26" r:id="rId190" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1"/>
-    <hyperlink ref="K26" r:id="rId191" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/4159pQjbgwL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId192" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
-    <hyperlink ref="M26" r:id="rId193" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N26" r:id="rId194"/>
-    <hyperlink ref="AW26" r:id="rId195" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UG91OLAXZDO3"/>
-    <hyperlink ref="C27" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
-    <hyperlink ref="G27" r:id="rId197" tooltip="https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J27" r:id="rId198" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1"/>
-    <hyperlink ref="K27" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
-    <hyperlink ref="M27" r:id="rId201" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N27" r:id="rId202"/>
-    <hyperlink ref="AW27" r:id="rId203" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09"/>
-    <hyperlink ref="C28" r:id="rId204" tooltip="https://www.amazon.co.jp/dp/B0H993XND4"/>
-    <hyperlink ref="G28" r:id="rId205" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Gwrv"/>
-    <hyperlink ref="J28" r:id="rId206" tooltip="https://www.amazon.co.jp/dp/B0H993XND4?psc=1"/>
-    <hyperlink ref="K28" r:id="rId207" tooltip="https://m.media-amazon.com/images/I/31OojZZwR0L._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0H993XND4"/>
-    <hyperlink ref="M28" r:id="rId209" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N28" r:id="rId210"/>
-    <hyperlink ref="AW28" r:id="rId211" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1KH8VSASY5CZN"/>
-    <hyperlink ref="C29" r:id="rId212" tooltip="https://www.amazon.co.jp/dp/B001AHMQ90"/>
-    <hyperlink ref="G29" r:id="rId213" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J29" r:id="rId214" tooltip="https://www.amazon.co.jp/dp/B001AHMQ90?psc=1"/>
-    <hyperlink ref="K29" r:id="rId215" tooltip="https://images-fe.ssl-images-amazon.com/images/I/81jZdnaokeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B001AHMQ90"/>
-    <hyperlink ref="C30" r:id="rId217" tooltip="https://www.amazon.co.jp/dp/B075MWCF8L"/>
-    <hyperlink ref="G30" r:id="rId218" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J30" r:id="rId219" tooltip="https://www.amazon.co.jp/dp/B075MWCF8L?psc=1"/>
-    <hyperlink ref="K30" r:id="rId220" tooltip="https://images-fe.ssl-images-amazon.com/images/I/710AEFYSgZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId221" tooltip="https://www.amazon.co.jp/dp/B075MWCF8L"/>
-    <hyperlink ref="C31" r:id="rId222" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
-    <hyperlink ref="G31" r:id="rId223" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J31" r:id="rId224" tooltip="https://www.amazon.co.jp/dp/B07KR2J116?psc=1"/>
-    <hyperlink ref="K31" r:id="rId225" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61+eOXLQJ5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
-    <hyperlink ref="C32" r:id="rId227" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
-    <hyperlink ref="G32" r:id="rId228" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J32" r:id="rId229" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
-    <hyperlink ref="K32" r:id="rId230" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31NELDCajpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId231" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
-    <hyperlink ref="C33" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
-    <hyperlink ref="G33" r:id="rId233" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J33" r:id="rId234" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
-    <hyperlink ref="K33" r:id="rId235" tooltip="https://images-fe.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
-    <hyperlink ref="C34" r:id="rId237" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="G34" r:id="rId238" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J34" r:id="rId239" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
-    <hyperlink ref="K34" r:id="rId240" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="C35" r:id="rId242" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
-    <hyperlink ref="G35" r:id="rId243" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J35" r:id="rId244" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
-    <hyperlink ref="K35" r:id="rId245" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
-    <hyperlink ref="C36" r:id="rId247" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
-    <hyperlink ref="G36" r:id="rId248" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J36" r:id="rId249" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1"/>
-    <hyperlink ref="K36" r:id="rId250" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71uxs5Aq9ML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId251" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
-    <hyperlink ref="C37" r:id="rId252" tooltip="https://www.amazon.co.jp/dp/B0CYZFT9GT"/>
-    <hyperlink ref="G37" r:id="rId253" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J37" r:id="rId254" tooltip="https://www.amazon.co.jp/dp/B0CYZFT9GT?psc=1"/>
-    <hyperlink ref="K37" r:id="rId255" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61im7zODi8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B0CYZFT9GT"/>
-    <hyperlink ref="C38" r:id="rId257" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
-    <hyperlink ref="G38" r:id="rId258" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J38" r:id="rId259" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1"/>
-    <hyperlink ref="K38" r:id="rId260" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71ZEEXdN4uL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId261" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
-    <hyperlink ref="C39" r:id="rId262" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
-    <hyperlink ref="G39" r:id="rId263" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J39" r:id="rId264" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1"/>
-    <hyperlink ref="K39" r:id="rId265" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId266" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
-    <hyperlink ref="C40" r:id="rId267" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
-    <hyperlink ref="G40" r:id="rId268" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J40" r:id="rId269" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
-    <hyperlink ref="K40" r:id="rId270" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
-    <hyperlink ref="C41" r:id="rId272" tooltip="https://www.amazon.co.jp/dp/B0FHP2HN6D"/>
-    <hyperlink ref="G41" r:id="rId273" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J41" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0FHP2HN6D?psc=1"/>
-    <hyperlink ref="K41" r:id="rId275" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71oZRUgvCTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0FHP2HN6D"/>
-    <hyperlink ref="C42" r:id="rId277" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
-    <hyperlink ref="G42" r:id="rId278" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J42" r:id="rId279" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1"/>
-    <hyperlink ref="K42" r:id="rId280" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
-    <hyperlink ref="C43" r:id="rId282" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
-    <hyperlink ref="G43" r:id="rId283" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
-    <hyperlink ref="K43" r:id="rId285" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
-    <hyperlink ref="M43" r:id="rId287" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N43" r:id="rId288"/>
-    <hyperlink ref="AW43" r:id="rId289" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC"/>
-    <hyperlink ref="C44" r:id="rId290" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="G44" r:id="rId291" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J44" r:id="rId292" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
-    <hyperlink ref="K44" r:id="rId293" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId294" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="C45" r:id="rId295" tooltip="https://www.amazon.co.jp/dp/B0FTLDNXKS"/>
-    <hyperlink ref="G45" r:id="rId296" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J45" r:id="rId297" tooltip="https://www.amazon.co.jp/dp/B0FTLDNXKS?psc=1"/>
-    <hyperlink ref="K45" r:id="rId298" tooltip="https://images-fe.ssl-images-amazon.com/images/I/2198xIu6DlL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId299" tooltip="https://www.amazon.co.jp/dp/B0FTLDNXKS"/>
-    <hyperlink ref="C46" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
-    <hyperlink ref="G46" r:id="rId301" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J46" r:id="rId302" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1"/>
-    <hyperlink ref="K46" r:id="rId303" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
-    <hyperlink ref="C47" r:id="rId305" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="G47" r:id="rId306" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J47" r:id="rId307" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
-    <hyperlink ref="K47" r:id="rId308" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61FvOi4+ZDL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId309" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="C48" r:id="rId310" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
-    <hyperlink ref="G48" r:id="rId311" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J48" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1"/>
-    <hyperlink ref="K48" r:id="rId313" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51OBVYbKFFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId314" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
-    <hyperlink ref="C49" r:id="rId315" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
-    <hyperlink ref="G49" r:id="rId316" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J49" r:id="rId317" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
-    <hyperlink ref="K49" r:id="rId318" tooltip="https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId319" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
-    <hyperlink ref="C50" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0HGQBZGVX"/>
-    <hyperlink ref="G50" r:id="rId321" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J50" r:id="rId322" tooltip="https://www.amazon.co.jp/dp/B0HGQBZGVX?psc=1"/>
-    <hyperlink ref="K50" r:id="rId323" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51sDx2mVMXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0HGQBZGVX"/>
-    <hyperlink ref="C51" r:id="rId325" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
-    <hyperlink ref="G51" r:id="rId326" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J51" r:id="rId327" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1"/>
-    <hyperlink ref="K51" r:id="rId328" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41ItordAnnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId329" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
+    <hyperlink ref="AW24" r:id="rId180" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09"/>
+    <hyperlink ref="C25" r:id="rId181" tooltip="https://www.amazon.co.jp/dp/B001AHMQ90"/>
+    <hyperlink ref="G25" r:id="rId182" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J25" r:id="rId183" tooltip="https://www.amazon.co.jp/dp/B001AHMQ90?psc=1"/>
+    <hyperlink ref="K25" r:id="rId184" tooltip="https://images-fe.ssl-images-amazon.com/images/I/81jZdnaokeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId185" tooltip="https://www.amazon.co.jp/dp/B001AHMQ90"/>
+    <hyperlink ref="C26" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B075MWCF8L"/>
+    <hyperlink ref="G26" r:id="rId187" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J26" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B075MWCF8L?psc=1"/>
+    <hyperlink ref="K26" r:id="rId189" tooltip="https://images-fe.ssl-images-amazon.com/images/I/710AEFYSgZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId190" tooltip="https://www.amazon.co.jp/dp/B075MWCF8L"/>
+    <hyperlink ref="C27" r:id="rId191" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
+    <hyperlink ref="G27" r:id="rId192" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J27" r:id="rId193" tooltip="https://www.amazon.co.jp/dp/B07KR2J116?psc=1"/>
+    <hyperlink ref="K27" r:id="rId194" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61+eOXLQJ5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId195" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
+    <hyperlink ref="C28" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="G28" r:id="rId197" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J28" r:id="rId198" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
+    <hyperlink ref="K28" r:id="rId199" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31NELDCajpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="C29" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
+    <hyperlink ref="G29" r:id="rId202" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J29" r:id="rId203" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
+    <hyperlink ref="K29" r:id="rId204" tooltip="https://images-fe.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId205" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
+    <hyperlink ref="C30" r:id="rId206" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
+    <hyperlink ref="G30" r:id="rId207" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J30" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
+    <hyperlink ref="K30" r:id="rId209" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
+    <hyperlink ref="C31" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="G31" r:id="rId212" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J31" r:id="rId213" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
+    <hyperlink ref="K31" r:id="rId214" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="C32" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
+    <hyperlink ref="G32" r:id="rId217" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J32" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1"/>
+    <hyperlink ref="K32" r:id="rId219" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71uxs5Aq9ML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
+    <hyperlink ref="C33" r:id="rId221" tooltip="https://www.amazon.co.jp/dp/B0CYZFT9GT"/>
+    <hyperlink ref="G33" r:id="rId222" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J33" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B0CYZFT9GT?psc=1"/>
+    <hyperlink ref="K33" r:id="rId224" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61im7zODi8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B0CYZFT9GT"/>
+    <hyperlink ref="C34" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
+    <hyperlink ref="G34" r:id="rId227" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J34" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1"/>
+    <hyperlink ref="K34" r:id="rId229" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71ZEEXdN4uL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
+    <hyperlink ref="C35" r:id="rId231" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
+    <hyperlink ref="G35" r:id="rId232" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J35" r:id="rId233" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1"/>
+    <hyperlink ref="K35" r:id="rId234" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId235" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
+    <hyperlink ref="C36" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="G36" r:id="rId237" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J36" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
+    <hyperlink ref="K36" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="C37" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
+    <hyperlink ref="G37" r:id="rId242" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J37" r:id="rId243" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1"/>
+    <hyperlink ref="K37" r:id="rId244" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
+    <hyperlink ref="C38" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="G38" r:id="rId247" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FL2KXDMX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
+    <hyperlink ref="K38" r:id="rId249" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="M38" r:id="rId251" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N38" r:id="rId252"/>
+    <hyperlink ref="AW38" r:id="rId253" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H1H068FIXKEC"/>
+    <hyperlink ref="C39" r:id="rId254" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="G39" r:id="rId255" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J39" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
+    <hyperlink ref="K39" r:id="rId257" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="C40" r:id="rId259" tooltip="https://www.amazon.co.jp/dp/B0FTLDNXKS"/>
+    <hyperlink ref="G40" r:id="rId260" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J40" r:id="rId261" tooltip="https://www.amazon.co.jp/dp/B0FTLDNXKS?psc=1"/>
+    <hyperlink ref="K40" r:id="rId262" tooltip="https://images-fe.ssl-images-amazon.com/images/I/2198xIu6DlL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId263" tooltip="https://www.amazon.co.jp/dp/B0FTLDNXKS"/>
+    <hyperlink ref="C41" r:id="rId264" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
+    <hyperlink ref="G41" r:id="rId265" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J41" r:id="rId266" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1"/>
+    <hyperlink ref="K41" r:id="rId267" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71VTbXxSMwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId268" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
+    <hyperlink ref="C42" r:id="rId269" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
+    <hyperlink ref="G42" r:id="rId270" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J42" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
+    <hyperlink ref="K42" r:id="rId272" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61FvOi4+ZDL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
+    <hyperlink ref="C43" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
+    <hyperlink ref="G43" r:id="rId275" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J43" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1"/>
+    <hyperlink ref="K43" r:id="rId277" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51OBVYbKFFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
+    <hyperlink ref="C44" r:id="rId279" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
+    <hyperlink ref="G44" r:id="rId280" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J44" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
+    <hyperlink ref="K44" r:id="rId282" tooltip="https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
+    <hyperlink ref="C45" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
+    <hyperlink ref="G45" r:id="rId285" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J45" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1"/>
+    <hyperlink ref="K45" r:id="rId287" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41ItordAnnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
   </hyperlinks>
-  <drawing r:id="rId330"/>
+  <drawing r:id="rId289"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -16225,7 +14860,7 @@
         <v>59256.75748502994</v>
       </c>
       <c r="G2" s="19">
-        <v>0.1308264786525656</v>
+        <v>0.13761845900288422</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16246,7 +14881,7 @@
         <v>43976.62337662338</v>
       </c>
       <c r="G3" s="19">
-        <v>0.0754014884449667</v>
+        <v>0.07931602801812938</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16267,7 +14902,7 @@
         <v>35800.0</v>
       </c>
       <c r="G4" s="19">
-        <v>0.06580493537015276</v>
+        <v>0.069221260815822</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16288,7 +14923,7 @@
         <v>4596.726526423807</v>
       </c>
       <c r="G5" s="19">
-        <v>0.38170779475127303</v>
+        <v>0.4015245158632056</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16309,7 +14944,7 @@
         <v>28597.19801980198</v>
       </c>
       <c r="G6" s="19">
-        <v>0.05934195064629847</v>
+        <v>0.06242274412855377</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16330,7 +14965,7 @@
         <v>15955.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.08793576184880533</v>
+        <v>0.09250103007828595</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16351,7 +14986,7 @@
         <v>50338.622641509435</v>
       </c>
       <c r="G8" s="19">
-        <v>0.020759890325107718</v>
+        <v>0.021837659662134322</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16372,7 +15007,7 @@
         <v>8999.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.06423815119467294</v>
+        <v>0.06757313555830242</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16393,235 +15028,151 @@
         <v>74800.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.004896200548374461</v>
+        <v>0.005150391429748661</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス</t>
+          <t>MOVA</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="C11" s="13">
-        <v>1726340</v>
+        <v>1307039</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13">
-        <v>12980.0</v>
+        <v>31879.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.026047786917352135</v>
+        <v>0.008446641944787803</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>MOVA</t>
+          <t>NARWAL(ナーワル)</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C12" s="13">
-        <v>1307039</v>
+        <v>527688</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>31879.0</v>
+        <v>58632.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.008029768899334117</v>
+        <v>0.001854140914709518</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>パオック(PAOCK)</t>
+          <t>SOLEMOOD</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="C13" s="13">
-        <v>897858</v>
+        <v>499257</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>11511.0</v>
+        <v>15129.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.01527614571092832</v>
+        <v>0.006798516687268232</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>NARWAL(ナーワル)</t>
+          <t>山善(YAMAZEN)</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="C14" s="13">
-        <v>527688</v>
+        <v>437320</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13">
-        <v>58632.0</v>
+        <v>3364.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.0017626321974148062</v>
+        <v>0.026782035434693038</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>SOLEMOOD</t>
+          <t>Vittorio(ヴィットリオ)</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C15" s="13">
-        <v>499257</v>
+        <v>418880</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13">
-        <v>15129.0</v>
+        <v>6545.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.006462984723854289</v>
+        <v>0.013185002060156572</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>longsafe</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C16" s="13">
-        <v>448362</v>
+        <v>326508</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13">
-        <v>11799.0</v>
+        <v>11661.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.007442224833529181</v>
+        <v>0.0057684384013185</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>山善(YAMAZEN)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B17" s="13">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C17" s="13">
-        <v>437320</v>
+        <v>0</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="13">
-        <v>3364.0</v>
-      </c>
+      <c r="F17" s="13"/>
       <c r="G17" s="19">
-        <v>0.0254602428515472</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Vittorio(ヴィットリオ)</t>
-        </is>
-      </c>
-      <c r="B18" s="13">
-        <v>64</v>
-      </c>
-      <c r="C18" s="13">
-        <v>418880</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13">
-        <v>6545.0</v>
-      </c>
-      <c r="G18" s="19">
-        <v>0.01253427340383862</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>uwant</t>
-        </is>
-      </c>
-      <c r="B19" s="13">
-        <v>28</v>
-      </c>
-      <c r="C19" s="13">
-        <v>326508</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13">
-        <v>11661.0</v>
-      </c>
-      <c r="G19" s="19">
-        <v>0.005483744614179397</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Gwrv</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
-        <v>3</v>
-      </c>
-      <c r="C20" s="13">
-        <v>25197</v>
-      </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13">
-        <v>8399.0</v>
-      </c>
-      <c r="G20" s="19">
-        <v>0.0005875440658049354</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B21" s="13">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -16633,7 +15184,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -16686,18 +15237,18 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <v>1244</v>
+        <v>1166</v>
       </c>
       <c r="C2" s="13">
-        <v>44448941</v>
+        <v>43551083</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13">
-        <v>35730.65996784566</v>
+        <v>37350.843053173245</v>
       </c>
       <c r="G2" s="19">
-        <v>0.2436349392871132</v>
+        <v>0.24021425628347753</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16718,7 +15269,7 @@
         <v>50804.18410041841</v>
       </c>
       <c r="G3" s="19">
-        <v>0.04680767724245985</v>
+        <v>0.0492377420683972</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16739,7 +15290,7 @@
         <v>35800.0</v>
       </c>
       <c r="G4" s="19">
-        <v>0.06580493537015276</v>
+        <v>0.069221260815822</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16760,7 +15311,7 @@
         <v>4596.726526423807</v>
       </c>
       <c r="G5" s="19">
-        <v>0.38170779475127303</v>
+        <v>0.4015245158632056</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16781,7 +15332,7 @@
         <v>28597.19801980198</v>
       </c>
       <c r="G6" s="19">
-        <v>0.05934195064629847</v>
+        <v>0.06242274412855377</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16802,7 +15353,7 @@
         <v>50338.622641509435</v>
       </c>
       <c r="G7" s="19">
-        <v>0.020759890325107718</v>
+        <v>0.021837659662134322</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16823,7 +15374,7 @@
         <v>32800.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.028593811202506855</v>
+        <v>0.030078285949732178</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16844,7 +15395,7 @@
         <v>29741.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.030160595377986682</v>
+        <v>0.03172641120725175</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16865,7 +15416,7 @@
         <v>8999.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.06423815119467294</v>
+        <v>0.06757313555830242</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16886,170 +15437,107 @@
         <v>74800.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.004896200548374461</v>
+        <v>0.005150391429748661</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス【9月の連休について 休業日：9/20～9/23 ※ご注文は9/24より順次出荷】</t>
+          <t>MOVA Official</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="C12" s="13">
-        <v>1726340</v>
+        <v>1307039</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>12980.0</v>
+        <v>31879.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.026047786917352135</v>
+        <v>0.008446641944787803</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>MOVA Official</t>
+          <t>SOLEMOOD正規販売店</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C13" s="13">
-        <v>1307039</v>
+        <v>499257</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>31879.0</v>
+        <v>15129.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.008029768899334117</v>
+        <v>0.006798516687268232</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>SOLEMOOD正規販売店</t>
+          <t>Uwant公式ストア</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C14" s="13">
-        <v>499257</v>
+        <v>326508</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13">
-        <v>15129.0</v>
+        <v>11661.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.006462984723854289</v>
+        <v>0.0057684384013185</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>YSJAPAN</t>
+          <t>JONR JP</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C15" s="13">
-        <v>448362</v>
+        <v>0</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="13">
-        <v>11799.0</v>
-      </c>
+      <c r="F15" s="13"/>
       <c r="G15" s="19">
-        <v>0.007442224833529181</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Uwant公式ストア</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C16" s="13">
-        <v>326508</v>
+        <v>0</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="13">
-        <v>11661.0</v>
-      </c>
+      <c r="F16" s="13"/>
       <c r="G16" s="19">
-        <v>0.005483744614179397</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Gwrv直営店(5-9日以内にお届け)</t>
-        </is>
-      </c>
-      <c r="B17" s="13">
-        <v>3</v>
-      </c>
-      <c r="C17" s="13">
-        <v>25197</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13">
-        <v>8399.0</v>
-      </c>
-      <c r="G17" s="19">
-        <v>0.0005875440658049354</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>JONR JP</t>
-        </is>
-      </c>
-      <c r="B18" s="13">
-        <v>0</v>
-      </c>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B19" s="13">
-        <v>0</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="19">
         <v>0.0</v>
       </c>
     </row>

--- a/data/merged/2026-09-23/MERGED_JP_Wet-Dry-Floor-Washer_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_JP_Wet-Dry-Floor-Washer_2026-09-23.xlsx
@@ -6144,94 +6144,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId42" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Product 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId43" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Product 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6573,7 +6485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR45"/>
+  <dimension ref="A1:BR43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -14198,7 +14110,7 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0HGLFDYL5</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="D43" s="12"/>
@@ -14211,23 +14123,23 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) 吸尘器 无线 Dyson V12s Detect Slim Submarine (SV46 SU) 棒 手持式吸尘器 气旋 可用水擦拭 干式吸尘器 带充电支架 【从现在开始用水擦拭】 (New V8 slim)</t>
+          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
         </is>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51OBVYbKFFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0HGLFDYL5</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="M43" s="12"/>
@@ -14292,210 +14204,6 @@
       <c r="BP43" s="20"/>
       <c r="BQ43" s="20"/>
       <c r="BR43" s="11"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <v>43</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>B0HGLNPJPC</t>
-        </is>
-      </c>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
-        </is>
-      </c>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>B0HGLNPJPC</t>
-        </is>
-      </c>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="15"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="13"/>
-      <c r="U44" s="14"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="13"/>
-      <c r="AA44"/>
-      <c r="AB44"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="17"/>
-      <c r="AE44" s="13"/>
-      <c r="AF44" s="18"/>
-      <c r="AG44" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="13"/>
-      <c r="AI44" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="11"/>
-      <c r="AL44" s="17"/>
-      <c r="AM44" s="11"/>
-      <c r="AN44" s="11"/>
-      <c r="AO44" s="11"/>
-      <c r="AP44"/>
-      <c r="AQ44" s="17"/>
-      <c r="AR44" s="17"/>
-      <c r="AS44" s="12"/>
-      <c r="AT44" s="11"/>
-      <c r="AU44" s="11"/>
-      <c r="AV44" s="12"/>
-      <c r="AW44" s="11"/>
-      <c r="AX44" s="11"/>
-      <c r="AY44" s="11"/>
-      <c r="AZ44" s="11"/>
-      <c r="BA44" s="11"/>
-      <c r="BB44" s="11"/>
-      <c r="BC44" s="11"/>
-      <c r="BD44" s="11"/>
-      <c r="BE44" s="11"/>
-      <c r="BF44" s="11"/>
-      <c r="BG44" s="11"/>
-      <c r="BH44" s="12"/>
-      <c r="BI44" s="20"/>
-      <c r="BJ44" s="20"/>
-      <c r="BK44" s="20"/>
-      <c r="BL44" s="20"/>
-      <c r="BM44" s="20"/>
-      <c r="BN44" s="20"/>
-      <c r="BO44" s="20"/>
-      <c r="BP44" s="20"/>
-      <c r="BQ44" s="20"/>
-      <c r="BR44" s="11"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>B0HHN61KPZ</t>
-        </is>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>Dyson(ダイソン) Dyson V12s Detect Slim Submarine 无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
-        </is>
-      </c>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41ItordAnnL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>B0HHN61KPZ</t>
-        </is>
-      </c>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="14"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="13"/>
-      <c r="U45" s="14"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="13"/>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45" s="2"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="13"/>
-      <c r="AF45" s="18"/>
-      <c r="AG45" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="13"/>
-      <c r="AI45" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="11"/>
-      <c r="AL45" s="17"/>
-      <c r="AM45" s="11"/>
-      <c r="AN45" s="11"/>
-      <c r="AO45" s="11"/>
-      <c r="AP45"/>
-      <c r="AQ45" s="17"/>
-      <c r="AR45" s="17"/>
-      <c r="AS45" s="12"/>
-      <c r="AT45" s="11"/>
-      <c r="AU45" s="11"/>
-      <c r="AV45" s="12"/>
-      <c r="AW45" s="11"/>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11"/>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="11"/>
-      <c r="BB45" s="11"/>
-      <c r="BC45" s="11"/>
-      <c r="BD45" s="11"/>
-      <c r="BE45" s="11"/>
-      <c r="BF45" s="11"/>
-      <c r="BG45" s="11"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45" s="20"/>
-      <c r="BJ45" s="20"/>
-      <c r="BK45" s="20"/>
-      <c r="BL45" s="20"/>
-      <c r="BM45" s="20"/>
-      <c r="BN45" s="20"/>
-      <c r="BO45" s="20"/>
-      <c r="BP45" s="20"/>
-      <c r="BQ45" s="20"/>
-      <c r="BR45" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14774,23 +14482,13 @@
     <hyperlink ref="J42" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
     <hyperlink ref="K42" r:id="rId272" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61FvOi4+ZDL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L42" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="C43" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
+    <hyperlink ref="C43" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
     <hyperlink ref="G43" r:id="rId275" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J43" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1"/>
-    <hyperlink ref="K43" r:id="rId277" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51OBVYbKFFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
-    <hyperlink ref="C44" r:id="rId279" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
-    <hyperlink ref="G44" r:id="rId280" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J44" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
-    <hyperlink ref="K44" r:id="rId282" tooltip="https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
-    <hyperlink ref="C45" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
-    <hyperlink ref="G45" r:id="rId285" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J45" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1"/>
-    <hyperlink ref="K45" r:id="rId287" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41ItordAnnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
+    <hyperlink ref="J43" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
+    <hyperlink ref="K43" r:id="rId277" tooltip="https://images-fe.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
   </hyperlinks>
-  <drawing r:id="rId289"/>
+  <drawing r:id="rId279"/>
 </worksheet>
 </file>
 
